--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Casademont Zaragoza.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Casademont Zaragoza.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2202.6</v>
+        <v>2528.4</v>
       </c>
       <c r="C2" t="n">
-        <v>2197.54</v>
+        <v>2522.220000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>111.6248168406491</v>
+        <v>110.1014185915582</v>
       </c>
       <c r="E2" t="n">
-        <v>118.6781583042857</v>
+        <v>118.2291790565454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5355145413870246</v>
+        <v>0.5277242044358728</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1682176091624911</v>
+        <v>0.1699179706348659</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3226473629782833</v>
+        <v>0.3292144748455428</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3008948545861297</v>
+        <v>0.2835101253616201</v>
       </c>
       <c r="J2" t="n">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="L2" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="M2" t="n">
-        <v>391</v>
+        <v>453</v>
       </c>
       <c r="N2" t="n">
-        <v>951</v>
+        <v>1061</v>
       </c>
       <c r="O2" t="n">
-        <v>1269</v>
+        <v>1422</v>
       </c>
       <c r="P2" t="n">
-        <v>0.709731543624161</v>
+        <v>0.6856316297010607</v>
       </c>
       <c r="Q2" t="n">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="R2" t="n">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1616331096196868</v>
+        <v>0.1687560270009643</v>
       </c>
       <c r="T2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U2" t="n">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1375838926174497</v>
+        <v>0.1354869816779171</v>
       </c>
       <c r="W2" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="X2" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09451901565995526</v>
+        <v>0.09691417550626807</v>
       </c>
       <c r="Z2" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="AA2" t="n">
-        <v>505</v>
+        <v>580</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2824384787472036</v>
+        <v>0.2796528447444552</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7494089834515366</v>
+        <v>0.7461322081575246</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.42560553633218</v>
+        <v>0.4314285714285714</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3558718861209965</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4437869822485207</v>
+        <v>0.4378109452736318</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2891089108910891</v>
+        <v>0.2741379310344828</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.498817966903073</v>
+        <v>1.492264416315049</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.7117437722419929</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.983679525222552</v>
+        <v>0.9487836107554417</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8380281690140845</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.009615384615385</v>
+        <v>1.013404825737265</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.575</v>
+        <v>1.573643410852713</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.078014184397163</v>
+        <v>1.054766734279919</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.226950354609929</v>
+        <v>4.206896551724138</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.304964539007092</v>
+        <v>5.261663286004056</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.66428571428571</v>
+        <v>79.0125</v>
       </c>
       <c r="C3" t="n">
-        <v>78.48357142857144</v>
+        <v>78.81937500000004</v>
       </c>
       <c r="D3" t="n">
-        <v>111.6248168406491</v>
+        <v>110.1014185915582</v>
       </c>
       <c r="E3" t="n">
-        <v>118.6781583042857</v>
+        <v>118.2291790565454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5355145413870246</v>
+        <v>0.5277242044358728</v>
       </c>
       <c r="G3" t="n">
-        <v>0.168217609162491</v>
+        <v>0.1699179706348659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3226473629782833</v>
+        <v>0.3292144748455428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3008948545861297</v>
+        <v>0.2835101253616201</v>
       </c>
       <c r="J3" t="n">
-        <v>10.71428571428571</v>
+        <v>11.15625</v>
       </c>
       <c r="K3" t="n">
-        <v>11.25</v>
+        <v>11.8125</v>
       </c>
       <c r="L3" t="n">
-        <v>6.75</v>
+        <v>6.34375</v>
       </c>
       <c r="M3" t="n">
-        <v>13.96428571428571</v>
+        <v>14.15625</v>
       </c>
       <c r="N3" t="n">
-        <v>33.96428571428572</v>
+        <v>33.15625</v>
       </c>
       <c r="O3" t="n">
-        <v>45.32142857142857</v>
+        <v>44.4375</v>
       </c>
       <c r="P3" t="n">
-        <v>0.709731543624161</v>
+        <v>0.6856316297010607</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.392857142857143</v>
+        <v>4.71875</v>
       </c>
       <c r="R3" t="n">
-        <v>10.32142857142857</v>
+        <v>10.9375</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1616331096196868</v>
+        <v>0.1687560270009643</v>
       </c>
       <c r="T3" t="n">
-        <v>3.214285714285714</v>
+        <v>3.125</v>
       </c>
       <c r="U3" t="n">
-        <v>8.785714285714286</v>
+        <v>8.78125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1375838926174497</v>
+        <v>0.1354869816779171</v>
       </c>
       <c r="W3" t="n">
-        <v>2.678571428571428</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>6.035714285714286</v>
+        <v>6.28125</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09451901565995526</v>
+        <v>0.09691417550626807</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.214285714285714</v>
+        <v>4.96875</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.03571428571428</v>
+        <v>18.125</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2824384787472036</v>
+        <v>0.2796528447444552</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7494089834515367</v>
+        <v>0.7461322081575246</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.42560553633218</v>
+        <v>0.4314285714285714</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3558718861209965</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4437869822485207</v>
+        <v>0.4378109452736318</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2891089108910891</v>
+        <v>0.2741379310344828</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.498817966903073</v>
+        <v>1.492264416315049</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.7117437722419929</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.983679525222552</v>
+        <v>0.9487836107554417</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8380281690140845</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.009615384615385</v>
+        <v>1.013404825737265</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.575</v>
+        <v>1.573643410852713</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.078014184397163</v>
+        <v>1.054766734279919</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.226950354609929</v>
+        <v>4.206896551724138</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.304964539007091</v>
+        <v>5.261663286004056</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2192.48</v>
+        <v>2516.04</v>
       </c>
       <c r="C4" t="n">
-        <v>2197.54</v>
+        <v>2522.220000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>118.6781583042857</v>
+        <v>118.2291790565454</v>
       </c>
       <c r="E4" t="n">
-        <v>111.6248168406491</v>
+        <v>110.1014185915582</v>
       </c>
       <c r="F4" t="n">
-        <v>0.562365010799136</v>
+        <v>0.5672666982472762</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1396380581532667</v>
+        <v>0.1482234067723483</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3121272365805169</v>
+        <v>0.3159752868490733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2834773218142548</v>
+        <v>0.2780672666982473</v>
       </c>
       <c r="J4" t="n">
-        <v>430</v>
+        <v>492</v>
       </c>
       <c r="K4" t="n">
-        <v>320</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="M4" t="n">
-        <v>336</v>
+        <v>409</v>
       </c>
       <c r="N4" t="n">
-        <v>928</v>
+        <v>1042</v>
       </c>
       <c r="O4" t="n">
-        <v>1258</v>
+        <v>1395</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6792656587473002</v>
+        <v>0.6608242539081004</v>
       </c>
       <c r="Q4" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="R4" t="n">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="S4" t="n">
-        <v>0.148488120950324</v>
+        <v>0.1549028896257698</v>
       </c>
       <c r="T4" t="n">
+        <v>92</v>
+      </c>
+      <c r="U4" t="n">
+        <v>201</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.09521553765987684</v>
+      </c>
+      <c r="W4" t="n">
         <v>80</v>
       </c>
-      <c r="U4" t="n">
-        <v>180</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.09719222462203024</v>
-      </c>
-      <c r="W4" t="n">
-        <v>65</v>
-      </c>
       <c r="X4" t="n">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1042116630669546</v>
+        <v>0.1117953576504026</v>
       </c>
       <c r="Z4" t="n">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="AA4" t="n">
-        <v>638</v>
+        <v>718</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3444924406047516</v>
+        <v>0.3401231643770725</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7376788553259142</v>
+        <v>0.7469534050179212</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4218181818181818</v>
+        <v>0.4159021406727829</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4577114427860697</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3367875647668394</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3605015673981191</v>
+        <v>0.3662952646239555</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.475357710651828</v>
+        <v>1.493906810035842</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9154228855721394</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.064981949458484</v>
+        <v>1.078616352201258</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.016548463356974</v>
+        <v>0.9979716024340771</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.019108280254777</v>
+        <v>1.011173184357542</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.722689075630252</v>
+        <v>1.691275167785235</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.565714285714286</v>
+        <v>1.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.291428571428572</v>
+        <v>4.955399061032864</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.857142857142857</v>
+        <v>6.455399061032864</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.30285714285715</v>
+        <v>78.62624999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>78.48357142857144</v>
+        <v>78.81937500000004</v>
       </c>
       <c r="D5" t="n">
-        <v>118.6781583042857</v>
+        <v>118.2291790565454</v>
       </c>
       <c r="E5" t="n">
-        <v>111.6248168406491</v>
+        <v>110.1014185915582</v>
       </c>
       <c r="F5" t="n">
-        <v>0.562365010799136</v>
+        <v>0.5672666982472762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1396380581532667</v>
+        <v>0.1482234067723483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3121272365805169</v>
+        <v>0.3159752868490733</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2834773218142549</v>
+        <v>0.2780672666982473</v>
       </c>
       <c r="J5" t="n">
-        <v>15.35714285714286</v>
+        <v>15.375</v>
       </c>
       <c r="K5" t="n">
-        <v>11.42857142857143</v>
+        <v>11.3125</v>
       </c>
       <c r="L5" t="n">
-        <v>7.321428571428571</v>
+        <v>7.875</v>
       </c>
       <c r="M5" t="n">
-        <v>12</v>
+        <v>12.78125</v>
       </c>
       <c r="N5" t="n">
-        <v>33.14285714285715</v>
+        <v>32.5625</v>
       </c>
       <c r="O5" t="n">
-        <v>44.92857142857143</v>
+        <v>43.59375</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6792656587473003</v>
+        <v>0.6608242539081004</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.142857142857143</v>
+        <v>4.25</v>
       </c>
       <c r="R5" t="n">
-        <v>9.821428571428571</v>
+        <v>10.21875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.148488120950324</v>
+        <v>0.1549028896257698</v>
       </c>
       <c r="T5" t="n">
-        <v>2.857142857142857</v>
+        <v>2.875</v>
       </c>
       <c r="U5" t="n">
-        <v>6.428571428571429</v>
+        <v>6.28125</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09719222462203024</v>
+        <v>0.09521553765987684</v>
       </c>
       <c r="W5" t="n">
-        <v>2.321428571428572</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
-        <v>6.892857142857143</v>
+        <v>7.375</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1042116630669547</v>
+        <v>0.1117953576504026</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.214285714285714</v>
+        <v>8.21875</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.78571428571428</v>
+        <v>22.4375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3444924406047516</v>
+        <v>0.3401231643770725</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7376788553259142</v>
+        <v>0.7469534050179212</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4218181818181819</v>
+        <v>0.4159021406727829</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4577114427860697</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3367875647668394</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3605015673981191</v>
+        <v>0.3662952646239555</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.475357710651828</v>
+        <v>1.493906810035842</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9154228855721394</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.064981949458484</v>
+        <v>1.078616352201258</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.016548463356974</v>
+        <v>0.9979716024340771</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.019108280254777</v>
+        <v>1.011173184357542</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.722689075630252</v>
+        <v>1.691275167785235</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.565714285714286</v>
+        <v>1.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.291428571428571</v>
+        <v>4.955399061032864</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.857142857142857</v>
+        <v>6.455399061032864</v>
       </c>
     </row>
     <row r="7">
@@ -1419,156 +1419,156 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" t="n">
+        <v>203</v>
+      </c>
+      <c r="D8" t="n">
         <v>28</v>
       </c>
-      <c r="C8" t="n">
-        <v>156</v>
-      </c>
-      <c r="D8" t="n">
-        <v>20</v>
-      </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>63</v>
+      </c>
+      <c r="J8" t="n">
+        <v>117</v>
+      </c>
+      <c r="K8" t="n">
+        <v>41</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M8" t="n">
+        <v>35</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>49</v>
+      </c>
+      <c r="R8" t="n">
+        <v>73</v>
+      </c>
+      <c r="S8" t="n">
+        <v>69</v>
+      </c>
+      <c r="T8" t="n">
+        <v>248</v>
+      </c>
+      <c r="U8" t="n">
+        <v>26</v>
+      </c>
+      <c r="V8" t="n">
         <v>23</v>
       </c>
-      <c r="G8" t="n">
-        <v>80</v>
-      </c>
-      <c r="H8" t="n">
-        <v>47</v>
-      </c>
-      <c r="I8" t="n">
-        <v>55</v>
-      </c>
-      <c r="J8" t="n">
-        <v>98</v>
-      </c>
-      <c r="K8" t="n">
-        <v>37</v>
-      </c>
-      <c r="L8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" t="n">
-        <v>26</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>42</v>
-      </c>
-      <c r="R8" t="n">
-        <v>65</v>
-      </c>
-      <c r="S8" t="n">
-        <v>60</v>
-      </c>
-      <c r="T8" t="n">
-        <v>189</v>
-      </c>
-      <c r="U8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>14</v>
-      </c>
       <c r="W8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="Z8" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.766</v>
+        <v>0.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.176</v>
+        <v>0.24</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.294</v>
+        <v>0.263</v>
       </c>
       <c r="AH8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.462</v>
+        <v>0.45</v>
       </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.254</v>
+        <v>0.272</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>603:09</t>
+          <t>711:54</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>202.2</v>
+        <v>249.72</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.401</v>
+        <v>0.431</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.487</v>
+        <v>0.506</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.772</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.208</v>
+        <v>0.196</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.346</v>
+        <v>0.312</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.333</v>
+        <v>2.388</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.15</v>
+        <v>0.155</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.122</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="9">
@@ -1578,67 +1578,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="E9" t="n">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I9" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K9" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="Q9" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="R9" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="S9" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="T9" t="n">
-        <v>470</v>
+        <v>519</v>
       </c>
       <c r="U9" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="V9" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="W9" t="n">
         <v>34</v>
@@ -1647,87 +1647,87 @@
         <v>19</v>
       </c>
       <c r="Y9" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="Z9" t="n">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.79</v>
+        <v>0.793</v>
       </c>
       <c r="AB9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.413</v>
+        <v>0.426</v>
       </c>
       <c r="AE9" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AF9" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.407</v>
+        <v>0.411</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AK9" t="n">
         <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.333</v>
+        <v>0.261</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>726:20</t>
+          <t>826:01</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>366.84</v>
+        <v>421.36</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.608</v>
+        <v>0.603</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.639</v>
+        <v>0.631</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.118</v>
+        <v>1.092</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.125</v>
+        <v>0.135</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.29</v>
+        <v>0.269</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.63</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AV9" t="n">
         <v>0.226</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.188</v>
+        <v>0.181</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="10">
@@ -1737,100 +1737,100 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
+        <v>74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J10" t="n">
+        <v>89</v>
+      </c>
+      <c r="K10" t="n">
+        <v>34</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N10" t="n">
+        <v>26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>69</v>
       </c>
-      <c r="H10" t="n">
-        <v>64</v>
-      </c>
-      <c r="I10" t="n">
-        <v>78</v>
-      </c>
-      <c r="J10" t="n">
-        <v>81</v>
-      </c>
-      <c r="K10" t="n">
-        <v>32</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>17</v>
-      </c>
-      <c r="N10" t="n">
-        <v>21</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>59</v>
-      </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="R10" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="S10" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="T10" t="n">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="U10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="V10" t="n">
         <v>21</v>
       </c>
       <c r="W10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="Z10" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AA10" t="n">
         <v>0.752</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.294</v>
+        <v>0.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.182</v>
+        <v>0.286</v>
       </c>
       <c r="AH10" t="n">
         <v>5</v>
@@ -1842,51 +1842,51 @@
         <v>0.455</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.328</v>
+        <v>0.317</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>444:27</t>
+          <t>500:33</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>274.32</v>
+        <v>305.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.514</v>
+        <v>0.515</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.581</v>
+        <v>0.576</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.911</v>
+        <v>0.891</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.215</v>
+        <v>0.226</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.354</v>
+        <v>0.323</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.373</v>
+        <v>1.29</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.276</v>
+        <v>0.27</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.106</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="11">
@@ -2036,16 +2036,16 @@
         <v>0.545</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.229</v>
+        <v>0.227</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -2097,114 +2097,114 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="R12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="T12" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="U12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
+        <v>12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AE12" t="n">
         <v>10</v>
       </c>
-      <c r="X12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>8</v>
-      </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="AH12" t="n">
         <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.429</v>
+        <v>0.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL12" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.435</v>
+        <v>0.361</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>171:14</t>
+          <t>239:50</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>99.8</v>
+        <v>144.68</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.628</v>
+        <v>0.555</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.652</v>
+        <v>0.581</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.082</v>
+        <v>0.961</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.17</v>
+        <v>0.173</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.203</v>
+        <v>0.155</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.706</v>
+        <v>0.68</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.261</v>
+        <v>0.267</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.052</v>
+        <v>0.038</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="13">
@@ -2214,474 +2214,474 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
+        <v>513</v>
+      </c>
+      <c r="D13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E13" t="n">
+        <v>189</v>
+      </c>
+      <c r="F13" t="n">
+        <v>48</v>
+      </c>
+      <c r="G13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" t="n">
+        <v>149</v>
+      </c>
+      <c r="I13" t="n">
+        <v>178</v>
+      </c>
+      <c r="J13" t="n">
+        <v>57</v>
+      </c>
+      <c r="K13" t="n">
+        <v>92</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30</v>
+      </c>
+      <c r="M13" t="n">
+        <v>31</v>
+      </c>
+      <c r="N13" t="n">
+        <v>29</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>60</v>
+      </c>
+      <c r="R13" t="n">
+        <v>83</v>
+      </c>
+      <c r="S13" t="n">
+        <v>158</v>
+      </c>
+      <c r="T13" t="n">
+        <v>557</v>
+      </c>
+      <c r="U13" t="n">
+        <v>85</v>
+      </c>
+      <c r="V13" t="n">
+        <v>66</v>
+      </c>
+      <c r="W13" t="n">
+        <v>45</v>
+      </c>
+      <c r="X13" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>220</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>283</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="AB13" t="n">
         <v>28</v>
       </c>
-      <c r="C13" t="n">
-        <v>462</v>
-      </c>
-      <c r="D13" t="n">
-        <v>94</v>
-      </c>
-      <c r="E13" t="n">
-        <v>160</v>
-      </c>
-      <c r="F13" t="n">
-        <v>46</v>
-      </c>
-      <c r="G13" t="n">
-        <v>133</v>
-      </c>
-      <c r="H13" t="n">
-        <v>136</v>
-      </c>
-      <c r="I13" t="n">
-        <v>161</v>
-      </c>
-      <c r="J13" t="n">
-        <v>51</v>
-      </c>
-      <c r="K13" t="n">
-        <v>80</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26</v>
-      </c>
-      <c r="M13" t="n">
-        <v>25</v>
-      </c>
-      <c r="N13" t="n">
-        <v>25</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R13" t="n">
-        <v>72</v>
-      </c>
-      <c r="S13" t="n">
-        <v>143</v>
-      </c>
-      <c r="T13" t="n">
-        <v>512</v>
-      </c>
-      <c r="U13" t="n">
-        <v>70</v>
-      </c>
-      <c r="V13" t="n">
-        <v>59</v>
-      </c>
-      <c r="W13" t="n">
-        <v>43</v>
-      </c>
-      <c r="X13" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>197</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>249</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>22</v>
-      </c>
       <c r="AC13" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.458</v>
+        <v>0.491</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.458</v>
+        <v>0.407</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="AK13" t="n">
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.291</v>
+        <v>0.263</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>736:55</t>
+          <t>843:03</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>413.84</v>
+        <v>477.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.556</v>
+        <v>0.537</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.635</v>
+        <v>0.615</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.116</v>
+        <v>1.075</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.121</v>
+        <v>0.126</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.464</v>
+        <v>0.44</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="AV13" t="n">
         <v>0.251</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>#5 L. LANGARITA</t>
+          <t>#5 I. WASHINGTON</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>96</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>52</v>
+      </c>
+      <c r="H14" t="n">
         <v>7</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>182:30</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>99.08</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>#5 I. WASHINGTON</t>
+          <t>#5 L. LANGARITA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>162:15</t>
+          <t>00:57</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>91.08</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.546</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.569</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.988</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2691,156 +2691,156 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" t="n">
+        <v>137</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>52</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24</v>
+      </c>
+      <c r="G16" t="n">
+        <v>68</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>18</v>
+      </c>
+      <c r="J16" t="n">
         <v>28</v>
       </c>
-      <c r="C16" t="n">
-        <v>128</v>
-      </c>
-      <c r="D16" t="n">
-        <v>24</v>
-      </c>
-      <c r="E16" t="n">
-        <v>47</v>
-      </c>
-      <c r="F16" t="n">
-        <v>22</v>
-      </c>
-      <c r="G16" t="n">
-        <v>60</v>
-      </c>
-      <c r="H16" t="n">
-        <v>14</v>
-      </c>
-      <c r="I16" t="n">
-        <v>16</v>
-      </c>
-      <c r="J16" t="n">
-        <v>23</v>
-      </c>
       <c r="K16" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T16" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="U16" t="n">
+        <v>32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>15</v>
+      </c>
+      <c r="W16" t="n">
+        <v>12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y16" t="n">
         <v>29</v>
       </c>
-      <c r="V16" t="n">
-        <v>12</v>
-      </c>
-      <c r="W16" t="n">
-        <v>11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>27</v>
-      </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.75</v>
+        <v>0.744</v>
       </c>
       <c r="AB16" t="n">
         <v>5</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.353</v>
+        <v>0.316</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.333</v>
+        <v>0.324</v>
       </c>
       <c r="AK16" t="n">
         <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.394</v>
+        <v>0.382</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>536:16</t>
+          <t>593:00</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>124.04</v>
+        <v>138.92</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.533</v>
+        <v>0.508</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.535</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.032</v>
+        <v>0.986</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.131</v>
+        <v>0.125</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.3</v>
+        <v>2.545</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.651</v>
+        <v>0.661</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -3168,40 +3168,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>8</v>
@@ -3210,25 +3210,25 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R19" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="U19" t="n">
         <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="W19" t="n">
         <v>6</v>
@@ -3237,13 +3237,13 @@
         <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.844</v>
+        <v>0.872</v>
       </c>
       <c r="AB19" t="n">
         <v>2</v>
@@ -3255,69 +3255,69 @@
         <v>0.667</v>
       </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2</v>
       </c>
-      <c r="AG19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
       <c r="AI19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>234:40</t>
+          <t>277:54</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>55.16</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.512</v>
+        <v>0.615</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.652</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.115</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.163</v>
+        <v>0.145</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.275</v>
+        <v>0.25</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.778</v>
+        <v>0.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.089</v>
+        <v>0.106</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.148</v>
+        <v>0.135</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3467,35 +3467,35 @@
         <v>0.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>#12 J. SORIANO</t>
+          <t>#11 A. OLASENI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="D21" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3504,82 +3504,82 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="n">
         <v>33</v>
       </c>
-      <c r="I21" t="n">
-        <v>48</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="U21" t="n">
         <v>6</v>
       </c>
-      <c r="K21" t="n">
-        <v>32</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z21" t="n">
         <v>23</v>
       </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>14</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>18</v>
-      </c>
-      <c r="R21" t="n">
-        <v>33</v>
-      </c>
-      <c r="S21" t="n">
-        <v>31</v>
-      </c>
-      <c r="T21" t="n">
-        <v>130</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>26</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>82</v>
-      </c>
       <c r="AA21" t="n">
-        <v>0.671</v>
+        <v>0.826</v>
       </c>
       <c r="AB21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.552</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -3601,528 +3601,528 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>222:04</t>
+          <t>40:01</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>118.12</v>
+        <v>23.52</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.604</v>
+        <v>0.78</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.024</v>
+        <v>1.361</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.152</v>
+        <v>0.128</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.418</v>
+        <v>0.353</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.238</v>
+        <v>0.26</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.12</v>
+        <v>0.028</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.161</v>
+        <v>0.198</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>#14 B. DUBLJEVIC</t>
+          <t>#12 J. SORIANO</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>121</v>
+      </c>
+      <c r="D22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E22" t="n">
+        <v>79</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>33</v>
+      </c>
+      <c r="I22" t="n">
+        <v>48</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>32</v>
+      </c>
+      <c r="L22" t="n">
         <v>23</v>
       </c>
-      <c r="C22" t="n">
-        <v>185</v>
-      </c>
-      <c r="D22" t="n">
-        <v>46</v>
-      </c>
-      <c r="E22" t="n">
-        <v>85</v>
-      </c>
-      <c r="F22" t="n">
-        <v>13</v>
-      </c>
-      <c r="G22" t="n">
-        <v>54</v>
-      </c>
-      <c r="H22" t="n">
-        <v>54</v>
-      </c>
-      <c r="I22" t="n">
-        <v>66</v>
-      </c>
-      <c r="J22" t="n">
-        <v>40</v>
-      </c>
-      <c r="K22" t="n">
-        <v>90</v>
-      </c>
-      <c r="L22" t="n">
-        <v>57</v>
-      </c>
       <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
         <v>14</v>
       </c>
-      <c r="N22" t="n">
-        <v>13</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="R22" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="S22" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="T22" t="n">
-        <v>282</v>
+        <v>130</v>
       </c>
       <c r="U22" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="W22" t="n">
+        <v>2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>82</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="AE22" t="n">
         <v>6</v>
       </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>88</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>116</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2</v>
-      </c>
       <c r="AF22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>498:32</t>
+          <t>222:04</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>202.04</v>
+        <v>118.12</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.471</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.55</v>
+        <v>0.604</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.916</v>
+        <v>1.024</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.168</v>
+        <v>0.152</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.388</v>
+        <v>0.418</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.176</v>
+        <v>0.333</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.181</v>
+        <v>0.236</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.133</v>
+        <v>0.117</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.202</v>
+        <v>0.163</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.051</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>#15 J. RODRÍGUEZ</t>
+          <t>#14 B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" t="n">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
+        <v>59</v>
+      </c>
+      <c r="H23" t="n">
+        <v>62</v>
+      </c>
+      <c r="I23" t="n">
+        <v>77</v>
+      </c>
+      <c r="J23" t="n">
+        <v>45</v>
+      </c>
+      <c r="K23" t="n">
+        <v>106</v>
+      </c>
+      <c r="L23" t="n">
+        <v>70</v>
+      </c>
+      <c r="M23" t="n">
+        <v>17</v>
+      </c>
+      <c r="N23" t="n">
+        <v>13</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>40</v>
+      </c>
+      <c r="R23" t="n">
+        <v>62</v>
+      </c>
+      <c r="S23" t="n">
         <v>79</v>
       </c>
-      <c r="H23" t="n">
-        <v>41</v>
-      </c>
-      <c r="I23" t="n">
-        <v>51</v>
-      </c>
-      <c r="J23" t="n">
-        <v>74</v>
-      </c>
-      <c r="K23" t="n">
-        <v>72</v>
-      </c>
-      <c r="L23" t="n">
-        <v>15</v>
-      </c>
-      <c r="M23" t="n">
-        <v>31</v>
-      </c>
-      <c r="N23" t="n">
-        <v>22</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>49</v>
-      </c>
-      <c r="R23" t="n">
-        <v>60</v>
-      </c>
-      <c r="S23" t="n">
-        <v>52</v>
-      </c>
       <c r="T23" t="n">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V23" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="W23" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="Z23" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.678</v>
+        <v>0.737</v>
       </c>
       <c r="AB23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.484</v>
+        <v>0.367</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.255</v>
+        <v>0.182</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>566:26</t>
+          <t>584:39</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>262.44</v>
+        <v>226.88</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.505</v>
+        <v>0.448</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.548</v>
+        <v>0.532</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.892</v>
+        <v>0.877</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.187</v>
+        <v>0.176</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.215</v>
+        <v>0.405</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.51</v>
+        <v>1.125</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.207</v>
+        <v>0.172</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.031</v>
+        <v>0.136</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.142</v>
+        <v>0.206</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.097</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#17 C. ALÍAS</t>
+          <t>#15 J. RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="T24" t="n">
-        <v>-1</v>
+        <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.221</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>01:48</t>
+          <t>667:20</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>310.96</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>0.481</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>0.865</v>
       </c>
       <c r="AS24" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.604</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.249</v>
+        <v>0.206</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#18 A. SAVKOV</t>
+          <t>#17 C. ALÍAS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4137,46 +4137,46 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -4230,14 +4230,14 @@
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>01:48</t>
         </is>
       </c>
       <c r="AO25" t="n">
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.419</v>
+        <v>0.246</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -4277,422 +4277,422 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#20 D. STEPHENS</t>
+          <t>#18 A. SAVKOV</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>106</v>
+        <v>-2</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>328:02</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>90.28</v>
+        <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.141</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.123</v>
+        <v>0.415</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#21 C. KOUMADJE</t>
+          <t>#20 D. STEPHENS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>32</v>
+      </c>
+      <c r="L27" t="n">
+        <v>14</v>
+      </c>
+      <c r="M27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>10</v>
+      </c>
+      <c r="R27" t="n">
+        <v>29</v>
+      </c>
+      <c r="S27" t="n">
+        <v>14</v>
+      </c>
+      <c r="T27" t="n">
+        <v>106</v>
+      </c>
+      <c r="U27" t="n">
         <v>16</v>
       </c>
-      <c r="I27" t="n">
+      <c r="V27" t="n">
+        <v>18</v>
+      </c>
+      <c r="W27" t="n">
+        <v>4</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z27" t="n">
         <v>30</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>26</v>
-      </c>
-      <c r="L27" t="n">
-        <v>22</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="AA27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB27" t="n">
         <v>2</v>
       </c>
-      <c r="N27" t="n">
-        <v>11</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="AC27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI27" t="n">
         <v>14</v>
       </c>
-      <c r="Q27" t="n">
-        <v>14</v>
-      </c>
-      <c r="R27" t="n">
-        <v>32</v>
-      </c>
-      <c r="S27" t="n">
-        <v>22</v>
-      </c>
-      <c r="T27" t="n">
-        <v>78</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
+      <c r="AJ27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL27" t="n">
         <v>28</v>
       </c>
-      <c r="W27" t="n">
-        <v>2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>178:58</t>
+          <t>328:02</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>66.2</v>
+        <v>90.28</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.667</v>
+        <v>0.62</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.651</v>
+        <v>0.642</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.027</v>
+        <v>1.141</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.211</v>
+        <v>0.111</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.41</v>
+        <v>0.133</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.165</v>
+        <v>0.122</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.143</v>
+        <v>0.048</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.162</v>
+        <v>0.111</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#23 Y. TRAORÉ</t>
+          <t>#21 C. KOUMADJE</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>19</v>
+      </c>
+      <c r="C28" t="n">
+        <v>68</v>
+      </c>
+      <c r="D28" t="n">
+        <v>26</v>
+      </c>
+      <c r="E28" t="n">
+        <v>39</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>32</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>26</v>
+      </c>
+      <c r="L28" t="n">
         <v>22</v>
       </c>
-      <c r="C28" t="n">
-        <v>20</v>
-      </c>
-      <c r="D28" t="n">
-        <v>8</v>
-      </c>
-      <c r="E28" t="n">
-        <v>18</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>13</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>14</v>
+      </c>
+      <c r="R28" t="n">
+        <v>36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>23</v>
+      </c>
+      <c r="T28" t="n">
+        <v>73</v>
+      </c>
+      <c r="U28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" t="n">
-        <v>8</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="V28" t="n">
+        <v>28</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2</v>
+      </c>
+      <c r="X28" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
+      <c r="Y28" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
         <v>3</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>13</v>
-      </c>
-      <c r="S28" t="n">
-        <v>7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>7</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>3</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
@@ -4714,60 +4714,60 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>64:18</t>
+          <t>185:56</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>28.72</v>
+        <v>67.08</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.444</v>
+        <v>0.667</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.422</v>
+        <v>0.641</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.696</v>
+        <v>1.014</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.174</v>
+        <v>0.209</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.222</v>
+        <v>0.41</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.145</v>
+        <v>0.134</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#23 Y. TRAORÉ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4776,73 +4776,73 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
         <v>6</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4873,41 +4873,41 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>74:34</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>31.72</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="30">
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -4944,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4959,19 +4959,19 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
         <v>0</v>
@@ -5076,153 +5076,153 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>2453</v>
+        <v>2777</v>
       </c>
       <c r="D31" t="n">
-        <v>626</v>
+        <v>724</v>
       </c>
       <c r="E31" t="n">
-        <v>1114</v>
+        <v>1293</v>
       </c>
       <c r="F31" t="n">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="G31" t="n">
-        <v>674</v>
+        <v>781</v>
       </c>
       <c r="H31" t="n">
-        <v>538</v>
+        <v>588</v>
       </c>
       <c r="I31" t="n">
-        <v>690</v>
+        <v>760</v>
       </c>
       <c r="J31" t="n">
-        <v>456</v>
+        <v>520</v>
       </c>
       <c r="K31" t="n">
-        <v>692</v>
+        <v>775</v>
       </c>
       <c r="L31" t="n">
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="M31" t="n">
+        <v>246</v>
+      </c>
+      <c r="N31" t="n">
+        <v>192</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>493</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>453</v>
+      </c>
+      <c r="R31" t="n">
+        <v>734</v>
+      </c>
+      <c r="S31" t="n">
+        <v>715</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3096</v>
+      </c>
+      <c r="U31" t="n">
+        <v>357</v>
+      </c>
+      <c r="V31" t="n">
+        <v>378</v>
+      </c>
+      <c r="W31" t="n">
+        <v>203</v>
+      </c>
+      <c r="X31" t="n">
+        <v>129</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1061</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1422</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>151</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>350</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>281</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI31" t="n">
         <v>201</v>
       </c>
-      <c r="N31" t="n">
-        <v>169</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>423</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>391</v>
-      </c>
-      <c r="R31" t="n">
-        <v>647</v>
-      </c>
-      <c r="S31" t="n">
-        <v>633</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2753</v>
-      </c>
-      <c r="U31" t="n">
-        <v>300</v>
-      </c>
-      <c r="V31" t="n">
-        <v>315</v>
-      </c>
-      <c r="W31" t="n">
-        <v>189</v>
-      </c>
-      <c r="X31" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>951</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1269</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>123</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>289</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>246</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>169</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>0.444</v>
+        <v>0.438</v>
       </c>
       <c r="AK31" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="AL31" t="n">
-        <v>505</v>
+        <v>580</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.289</v>
+        <v>0.274</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>5625:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>2514.6</v>
+        <v>2901.4</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.536</v>
+        <v>0.528</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.586</v>
+        <v>0.577</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.976</v>
+        <v>0.957</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.168</v>
+        <v>0.17</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.301</v>
+        <v>0.284</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.078</v>
+        <v>1.055</v>
       </c>
       <c r="AV31" t="n">
         <v>0.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5235,153 +5235,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>2608</v>
+        <v>2982</v>
       </c>
       <c r="D32" t="n">
-        <v>599</v>
+        <v>683</v>
       </c>
       <c r="E32" t="n">
-        <v>1021</v>
+        <v>1157</v>
       </c>
       <c r="F32" t="n">
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="G32" t="n">
-        <v>831</v>
+        <v>954</v>
       </c>
       <c r="H32" t="n">
-        <v>525</v>
+        <v>587</v>
       </c>
       <c r="I32" t="n">
-        <v>692</v>
+        <v>766</v>
       </c>
       <c r="J32" t="n">
-        <v>548</v>
+        <v>639</v>
       </c>
       <c r="K32" t="n">
-        <v>655</v>
+        <v>760</v>
       </c>
       <c r="L32" t="n">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="M32" t="n">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="N32" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>350</v>
+        <v>426</v>
       </c>
       <c r="Q32" t="n">
-        <v>336</v>
+        <v>409</v>
       </c>
       <c r="R32" t="n">
-        <v>630</v>
+        <v>713</v>
       </c>
       <c r="S32" t="n">
-        <v>637</v>
+        <v>722</v>
       </c>
       <c r="T32" t="n">
-        <v>3066</v>
+        <v>3531</v>
       </c>
       <c r="U32" t="n">
-        <v>430</v>
+        <v>492</v>
       </c>
       <c r="V32" t="n">
-        <v>320</v>
+        <v>362</v>
       </c>
       <c r="W32" t="n">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="X32" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="Y32" t="n">
-        <v>928</v>
+        <v>1042</v>
       </c>
       <c r="Z32" t="n">
-        <v>1258</v>
+        <v>1395</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.738</v>
+        <v>0.747</v>
       </c>
       <c r="AB32" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="AC32" t="n">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.422</v>
+        <v>0.416</v>
       </c>
       <c r="AE32" t="n">
+        <v>92</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>201</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AH32" t="n">
         <v>80</v>
       </c>
-      <c r="AF32" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>65</v>
-      </c>
       <c r="AI32" t="n">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="AK32" t="n">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="AL32" t="n">
-        <v>638</v>
+        <v>718</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>5625:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>2506.48</v>
+        <v>2874.04</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.605</v>
+        <v>0.609</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.041</v>
+        <v>1.038</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.14</v>
+        <v>0.148</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.283</v>
+        <v>0.278</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.566</v>
+        <v>1.5</v>
       </c>
       <c r="AV32" t="n">
         <v>0.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -5447,319 +5447,319 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#0 M. SPISSU (Per Game)</t>
+          <t>#00 D. ROBINSON (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>5.571</v>
+        <v>14.375</v>
       </c>
       <c r="D34" t="n">
-        <v>0.714</v>
+        <v>5.406</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>8.718999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.821</v>
+        <v>0.312</v>
       </c>
       <c r="G34" t="n">
-        <v>2.857</v>
+        <v>1.031</v>
       </c>
       <c r="H34" t="n">
-        <v>1.679</v>
+        <v>2.625</v>
       </c>
       <c r="I34" t="n">
-        <v>1.964</v>
+        <v>3.719</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1.321</v>
+        <v>4.125</v>
       </c>
       <c r="L34" t="n">
-        <v>0.429</v>
+        <v>1.156</v>
       </c>
       <c r="M34" t="n">
-        <v>0.929</v>
+        <v>1.188</v>
       </c>
       <c r="N34" t="n">
-        <v>0.286</v>
+        <v>0.781</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.5</v>
+        <v>1.781</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>1.781</v>
       </c>
       <c r="R34" t="n">
-        <v>2.321</v>
+        <v>2.781</v>
       </c>
       <c r="S34" t="n">
-        <v>2.143</v>
+        <v>3.281</v>
       </c>
       <c r="T34" t="n">
-        <v>189</v>
+        <v>519</v>
       </c>
       <c r="U34" t="n">
-        <v>0.786</v>
+        <v>1.906</v>
       </c>
       <c r="V34" t="n">
-        <v>0.5</v>
+        <v>1.844</v>
       </c>
       <c r="W34" t="n">
-        <v>0.464</v>
+        <v>1.062</v>
       </c>
       <c r="X34" t="n">
-        <v>0.321</v>
+        <v>0.594</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.107</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.75</v>
+        <v>7.562</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.766</v>
+        <v>0.793</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.107</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.607</v>
+        <v>1.906</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.176</v>
+        <v>0.426</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.179</v>
+        <v>1.219</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.607</v>
+        <v>2.969</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.294</v>
+        <v>0.411</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.214</v>
+        <v>0.125</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.464</v>
+        <v>0.312</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.462</v>
+        <v>0.4</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.607</v>
+        <v>0.188</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.393</v>
+        <v>0.719</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.254</v>
+        <v>0.261</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>25:48</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.221</v>
+        <v>13.167</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.401</v>
+        <v>0.603</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.487</v>
+        <v>0.631</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.772</v>
+        <v>1.092</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.208</v>
+        <v>0.135</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.346</v>
+        <v>0.269</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.333</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.15</v>
+        <v>0.226</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.023</v>
+        <v>0.051</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.181</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.122</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#00 D. ROBINSON (Per Game)</t>
+          <t>#0 M. SPISSU (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C35" t="n">
-        <v>14.643</v>
+        <v>6.344</v>
       </c>
       <c r="D35" t="n">
-        <v>5.429</v>
+        <v>0.875</v>
       </c>
       <c r="E35" t="n">
-        <v>8.75</v>
+        <v>2.25</v>
       </c>
       <c r="F35" t="n">
-        <v>0.321</v>
+        <v>0.969</v>
       </c>
       <c r="G35" t="n">
-        <v>0.964</v>
+        <v>3.156</v>
       </c>
       <c r="H35" t="n">
-        <v>2.821</v>
+        <v>1.688</v>
       </c>
       <c r="I35" t="n">
-        <v>3.964</v>
+        <v>1.969</v>
       </c>
       <c r="J35" t="n">
-        <v>1.036</v>
+        <v>3.656</v>
       </c>
       <c r="K35" t="n">
-        <v>4.357</v>
+        <v>1.281</v>
       </c>
       <c r="L35" t="n">
-        <v>1.107</v>
+        <v>0.594</v>
       </c>
       <c r="M35" t="n">
-        <v>1.107</v>
+        <v>1.094</v>
       </c>
       <c r="N35" t="n">
-        <v>0.714</v>
+        <v>0.281</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.643</v>
+        <v>1.531</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.643</v>
+        <v>1.531</v>
       </c>
       <c r="R35" t="n">
-        <v>2.786</v>
+        <v>2.281</v>
       </c>
       <c r="S35" t="n">
-        <v>3.357</v>
+        <v>2.156</v>
       </c>
       <c r="T35" t="n">
-        <v>470</v>
+        <v>248</v>
       </c>
       <c r="U35" t="n">
-        <v>1.714</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V35" t="n">
-        <v>1.893</v>
+        <v>0.719</v>
       </c>
       <c r="W35" t="n">
-        <v>1.214</v>
+        <v>0.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0.679</v>
+        <v>0.344</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.321</v>
+        <v>2.219</v>
       </c>
       <c r="Z35" t="n">
-        <v>8</v>
+        <v>2.844</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.679</v>
+        <v>0.188</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.643</v>
+        <v>0.781</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.413</v>
+        <v>0.24</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.25</v>
+        <v>0.156</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.071</v>
+        <v>0.594</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.407</v>
+        <v>0.263</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.107</v>
+        <v>0.281</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.321</v>
+        <v>0.625</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.214</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.643</v>
+        <v>2.531</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.333</v>
+        <v>0.272</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>25:56</t>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>13.101</v>
+        <v>7.804</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.608</v>
+        <v>0.431</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.639</v>
+        <v>0.506</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.118</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.125</v>
+        <v>0.196</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.29</v>
+        <v>0.312</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.63</v>
+        <v>2.388</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.226</v>
+        <v>0.155</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.188</v>
+        <v>0.065</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.042</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="36">
@@ -5769,474 +5769,474 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C36" t="n">
-        <v>14.706</v>
+        <v>13.6</v>
       </c>
       <c r="D36" t="n">
-        <v>3.353</v>
+        <v>3.3</v>
       </c>
       <c r="E36" t="n">
-        <v>6.588</v>
+        <v>6.35</v>
       </c>
       <c r="F36" t="n">
-        <v>1.412</v>
+        <v>1.25</v>
       </c>
       <c r="G36" t="n">
-        <v>4.059</v>
+        <v>3.7</v>
       </c>
       <c r="H36" t="n">
-        <v>3.765</v>
+        <v>3.25</v>
       </c>
       <c r="I36" t="n">
-        <v>4.588</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>4.765</v>
+        <v>4.45</v>
       </c>
       <c r="K36" t="n">
-        <v>1.882</v>
+        <v>1.7</v>
       </c>
       <c r="L36" t="n">
-        <v>0.529</v>
+        <v>0.55</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N36" t="n">
-        <v>1.235</v>
+        <v>1.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.471</v>
+        <v>3.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.471</v>
+        <v>3.45</v>
       </c>
       <c r="R36" t="n">
-        <v>2.647</v>
+        <v>2.65</v>
       </c>
       <c r="S36" t="n">
-        <v>4.588</v>
+        <v>4.2</v>
       </c>
       <c r="T36" t="n">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="U36" t="n">
-        <v>2.765</v>
+        <v>2.45</v>
       </c>
       <c r="V36" t="n">
-        <v>1.235</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>0.824</v>
+        <v>0.8</v>
       </c>
       <c r="X36" t="n">
-        <v>0.647</v>
+        <v>0.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>6.412</v>
+        <v>5.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.529</v>
+        <v>7.65</v>
       </c>
       <c r="AA36" t="n">
         <v>0.752</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.588</v>
+        <v>0.6</v>
       </c>
       <c r="AC36" t="n">
         <v>2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.294</v>
+        <v>0.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.118</v>
+        <v>0.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.647</v>
+        <v>0.7</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.182</v>
+        <v>0.286</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.294</v>
+        <v>0.25</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.647</v>
+        <v>0.55</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.455</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.118</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="n">
-        <v>3.412</v>
+        <v>3.15</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.328</v>
+        <v>0.317</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>26:08</t>
+          <t>25:01</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>16.136</v>
+        <v>15.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.514</v>
+        <v>0.515</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.581</v>
+        <v>0.576</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.911</v>
+        <v>0.891</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.215</v>
+        <v>0.226</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.354</v>
+        <v>0.323</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.373</v>
+        <v>1.29</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.276</v>
+        <v>0.27</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.187</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#3 E. STEVENSON (Per Game)</t>
+          <t>#3 WRIGHT-FOREMAN (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>4.778</v>
+        <v>11.583</v>
       </c>
       <c r="D37" t="n">
+        <v>3.083</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="T37" t="n">
+        <v>103</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="W37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" t="n">
+      <c r="X37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.917</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.222</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.222</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.444</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="T37" t="n">
-        <v>28</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="AG37" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI37" t="n">
         <v>0.833</v>
       </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.667</v>
+        <v>1.083</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.333</v>
+        <v>3</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.286</v>
+        <v>0.361</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>6.084</v>
+        <v>12.057</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.464</v>
+        <v>0.555</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.491</v>
+        <v>0.581</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.785</v>
+        <v>0.961</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.201</v>
+        <v>0.173</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.095</v>
+        <v>0.155</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.545</v>
+        <v>0.68</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.229</v>
+        <v>0.267</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.126</v>
+        <v>0.038</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.023</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#3 WRIGHT-FOREMAN (Per Game)</t>
+          <t>#3 E. STEVENSON (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" t="n">
-        <v>13.5</v>
+        <v>4.778</v>
       </c>
       <c r="D38" t="n">
-        <v>3.375</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>1.625</v>
+        <v>0.778</v>
       </c>
       <c r="G38" t="n">
-        <v>3.75</v>
+        <v>2.667</v>
       </c>
       <c r="H38" t="n">
-        <v>1.875</v>
+        <v>0.444</v>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>0.444</v>
       </c>
       <c r="J38" t="n">
-        <v>1.5</v>
+        <v>0.667</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5</v>
+        <v>0.222</v>
       </c>
       <c r="M38" t="n">
-        <v>0.625</v>
+        <v>0.556</v>
       </c>
       <c r="N38" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.125</v>
+        <v>1.222</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.125</v>
+        <v>1.222</v>
       </c>
       <c r="R38" t="n">
-        <v>1.75</v>
+        <v>1.444</v>
       </c>
       <c r="S38" t="n">
-        <v>2.375</v>
+        <v>0.889</v>
       </c>
       <c r="T38" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="U38" t="n">
-        <v>2.125</v>
+        <v>0.556</v>
       </c>
       <c r="V38" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>0.667</v>
       </c>
       <c r="X38" t="n">
-        <v>0.625</v>
+        <v>0.222</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.875</v>
+        <v>1.111</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.125</v>
+        <v>1.333</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.756</v>
+        <v>0.833</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.875</v>
+        <v>0.333</v>
       </c>
       <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.429</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AH38" t="n">
-        <v>0.375</v>
+        <v>0.111</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.875</v>
+        <v>0.333</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.25</v>
+        <v>0.667</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.875</v>
+        <v>2.333</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.435</v>
+        <v>0.286</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>12.475</v>
+        <v>6.084</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.628</v>
+        <v>0.464</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.652</v>
+        <v>0.491</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.082</v>
+        <v>0.785</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.17</v>
+        <v>0.201</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.203</v>
+        <v>0.095</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.706</v>
+        <v>0.545</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.261</v>
+        <v>0.227</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.052</v>
+        <v>0.127</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.059</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="39">
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>16.5</v>
+        <v>16.031</v>
       </c>
       <c r="D39" t="n">
-        <v>3.357</v>
+        <v>3.438</v>
       </c>
       <c r="E39" t="n">
-        <v>5.714</v>
+        <v>5.906</v>
       </c>
       <c r="F39" t="n">
-        <v>1.643</v>
+        <v>1.5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.75</v>
+        <v>4.688</v>
       </c>
       <c r="H39" t="n">
-        <v>4.857</v>
+        <v>4.656</v>
       </c>
       <c r="I39" t="n">
-        <v>5.75</v>
+        <v>5.562</v>
       </c>
       <c r="J39" t="n">
-        <v>1.821</v>
+        <v>1.781</v>
       </c>
       <c r="K39" t="n">
-        <v>2.857</v>
+        <v>2.875</v>
       </c>
       <c r="L39" t="n">
-        <v>0.929</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>0.893</v>
+        <v>0.969</v>
       </c>
       <c r="N39" t="n">
-        <v>0.893</v>
+        <v>0.906</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.786</v>
+        <v>1.875</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.786</v>
+        <v>1.875</v>
       </c>
       <c r="R39" t="n">
-        <v>2.571</v>
+        <v>2.594</v>
       </c>
       <c r="S39" t="n">
-        <v>5.107</v>
+        <v>4.938</v>
       </c>
       <c r="T39" t="n">
-        <v>512</v>
+        <v>557</v>
       </c>
       <c r="U39" t="n">
-        <v>2.5</v>
+        <v>2.656</v>
       </c>
       <c r="V39" t="n">
-        <v>2.107</v>
+        <v>2.062</v>
       </c>
       <c r="W39" t="n">
-        <v>1.536</v>
+        <v>1.406</v>
       </c>
       <c r="X39" t="n">
-        <v>1.214</v>
+        <v>1.094</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.036</v>
+        <v>6.875</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.893000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.791</v>
+        <v>0.777</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.786</v>
+        <v>0.875</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.714</v>
+        <v>1.781</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.458</v>
+        <v>0.491</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.393</v>
+        <v>0.344</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.857</v>
+        <v>0.844</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.458</v>
+        <v>0.407</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.571</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.071</v>
+        <v>1.125</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.071</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.679</v>
+        <v>3.562</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.291</v>
+        <v>0.263</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>26:19</t>
+          <t>26:20</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>14.78</v>
+        <v>14.916</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.556</v>
+        <v>0.537</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.635</v>
+        <v>0.615</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.116</v>
+        <v>1.075</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.121</v>
+        <v>0.126</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.464</v>
+        <v>0.44</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="AV39" t="n">
         <v>0.251</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>7.385</v>
       </c>
       <c r="D40" t="n">
-        <v>1.6</v>
+        <v>1.231</v>
       </c>
       <c r="E40" t="n">
-        <v>2.8</v>
+        <v>2.462</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7</v>
+        <v>1.462</v>
       </c>
       <c r="G40" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7</v>
+        <v>0.538</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.538</v>
       </c>
       <c r="J40" t="n">
-        <v>2.1</v>
+        <v>1.692</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4</v>
+        <v>0.385</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4</v>
+        <v>0.308</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2</v>
+        <v>0.231</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.2</v>
+        <v>0.923</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.2</v>
+        <v>0.923</v>
       </c>
       <c r="R40" t="n">
-        <v>1.9</v>
+        <v>1.615</v>
       </c>
       <c r="S40" t="n">
-        <v>0.9</v>
+        <v>0.769</v>
       </c>
       <c r="T40" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U40" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>0.5</v>
       </c>
-      <c r="V40" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.444</v>
-      </c>
       <c r="AK40" t="n">
-        <v>1.3</v>
+        <v>1.077</v>
       </c>
       <c r="AL40" t="n">
-        <v>3.9</v>
+        <v>3.231</v>
       </c>
       <c r="AM40" t="n">
         <v>0.333</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>9.108000000000001</v>
+        <v>7.622</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.546</v>
+        <v>0.53</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.569</v>
+        <v>0.551</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.988</v>
+        <v>0.969</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.132</v>
+        <v>0.121</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.092</v>
+        <v>0.083</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.75</v>
+        <v>1.833</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.251</v>
+        <v>0.24</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.078</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="41">
@@ -6723,156 +6723,156 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C42" t="n">
-        <v>4.571</v>
+        <v>4.281</v>
       </c>
       <c r="D42" t="n">
-        <v>0.857</v>
+        <v>0.781</v>
       </c>
       <c r="E42" t="n">
-        <v>1.679</v>
+        <v>1.625</v>
       </c>
       <c r="F42" t="n">
-        <v>0.786</v>
+        <v>0.75</v>
       </c>
       <c r="G42" t="n">
-        <v>2.143</v>
+        <v>2.125</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="I42" t="n">
-        <v>0.571</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>0.821</v>
+        <v>0.875</v>
       </c>
       <c r="K42" t="n">
-        <v>2.071</v>
+        <v>1.969</v>
       </c>
       <c r="L42" t="n">
-        <v>1.071</v>
+        <v>1.094</v>
       </c>
       <c r="M42" t="n">
-        <v>0.643</v>
+        <v>0.656</v>
       </c>
       <c r="N42" t="n">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="R42" t="n">
-        <v>2.179</v>
+        <v>2.188</v>
       </c>
       <c r="S42" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="T42" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="U42" t="n">
-        <v>1.036</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>0.429</v>
+        <v>0.469</v>
       </c>
       <c r="W42" t="n">
-        <v>0.393</v>
+        <v>0.375</v>
       </c>
       <c r="X42" t="n">
         <v>0.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.964</v>
+        <v>0.906</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.286</v>
+        <v>1.219</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.75</v>
+        <v>0.744</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.179</v>
+        <v>0.156</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.357</v>
+        <v>0.375</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.214</v>
+        <v>0.188</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.607</v>
+        <v>0.594</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.353</v>
+        <v>0.316</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.321</v>
+        <v>0.344</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.964</v>
+        <v>1.062</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.333</v>
+        <v>0.324</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.464</v>
+        <v>0.406</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.179</v>
+        <v>1.062</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.394</v>
+        <v>0.382</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>4.43</v>
+        <v>4.341</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.533</v>
+        <v>0.508</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.535</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.032</v>
+        <v>0.986</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.131</v>
+        <v>0.125</v>
       </c>
       <c r="AU42" t="n">
-        <v>2.3</v>
+        <v>2.545</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="43">
@@ -7181,13 +7181,13 @@
         <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="AW44" t="n">
         <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.651</v>
+        <v>0.661</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -7200,25 +7200,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C45" t="n">
-        <v>1.857</v>
+        <v>2.406</v>
       </c>
       <c r="D45" t="n">
-        <v>0.679</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>0.821</v>
+        <v>0.969</v>
       </c>
       <c r="F45" t="n">
-        <v>0.036</v>
+        <v>0.125</v>
       </c>
       <c r="G45" t="n">
-        <v>0.607</v>
+        <v>0.656</v>
       </c>
       <c r="H45" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="I45" t="n">
         <v>0.5</v>
@@ -7227,129 +7227,129 @@
         <v>0.25</v>
       </c>
       <c r="K45" t="n">
-        <v>1.107</v>
+        <v>1.031</v>
       </c>
       <c r="L45" t="n">
-        <v>0.643</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>0.286</v>
+        <v>0.312</v>
       </c>
       <c r="N45" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.321</v>
+        <v>0.312</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.321</v>
+        <v>0.312</v>
       </c>
       <c r="R45" t="n">
-        <v>1.607</v>
+        <v>1.625</v>
       </c>
       <c r="S45" t="n">
-        <v>0.464</v>
+        <v>0.438</v>
       </c>
       <c r="T45" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="U45" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="V45" t="n">
-        <v>0.393</v>
+        <v>0.656</v>
       </c>
       <c r="W45" t="n">
-        <v>0.214</v>
+        <v>0.188</v>
       </c>
       <c r="X45" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.964</v>
+        <v>1.062</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.143</v>
+        <v>1.219</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.844</v>
+        <v>0.872</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="AD45" t="n">
         <v>0.667</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.036</v>
+        <v>0.094</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.357</v>
+        <v>0.406</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.036</v>
+        <v>0.062</v>
       </c>
       <c r="AL45" t="n">
         <v>0.25</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>1.97</v>
+        <v>2.158</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.513</v>
+        <v>0.615</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.652</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.115</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.163</v>
+        <v>0.145</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.275</v>
+        <v>0.25</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.778</v>
+        <v>0.8</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.089</v>
+        <v>0.106</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.148</v>
+        <v>0.135</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -7499,13 +7499,13 @@
         <v>0.75</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AY46" t="n">
         <v>0.036</v>
@@ -7514,20 +7514,20 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#12 J. SORIANO (Per Game)</t>
+          <t>#11 A. OLASENI (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
         <v>16</v>
       </c>
-      <c r="C47" t="n">
-        <v>7.562</v>
-      </c>
       <c r="D47" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="E47" t="n">
-        <v>4.938</v>
+        <v>8.5</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -7536,82 +7536,82 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.062</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>33</v>
+      </c>
+      <c r="U47" t="n">
         <v>3</v>
       </c>
-      <c r="J47" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.438</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="R47" t="n">
-        <v>2.062</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="T47" t="n">
-        <v>130</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.25</v>
-      </c>
       <c r="V47" t="n">
-        <v>1.625</v>
+        <v>2.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.438</v>
+        <v>9.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.125</v>
+        <v>11.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.671</v>
+        <v>0.826</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.812</v>
+        <v>0.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.552</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
@@ -7633,528 +7633,528 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>7.382</v>
+        <v>11.76</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.604</v>
+        <v>0.78</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.024</v>
+        <v>1.361</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.152</v>
+        <v>0.128</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.418</v>
+        <v>0.353</v>
       </c>
       <c r="AU47" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.238</v>
+        <v>0.26</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.12</v>
+        <v>0.028</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.161</v>
+        <v>0.198</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#14 B. DUBLJEVIC (Per Game)</t>
+          <t>#12 J. SORIANO (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>8.042999999999999</v>
+        <v>7.562</v>
       </c>
       <c r="D48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4.938</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="E48" t="n">
-        <v>3.696</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.739</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3.913</v>
-      </c>
       <c r="L48" t="n">
-        <v>2.478</v>
+        <v>1.438</v>
       </c>
       <c r="M48" t="n">
-        <v>0.609</v>
+        <v>0.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.478</v>
+        <v>1.125</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.478</v>
+        <v>1.125</v>
       </c>
       <c r="R48" t="n">
-        <v>2.435</v>
+        <v>2.062</v>
       </c>
       <c r="S48" t="n">
-        <v>2.826</v>
+        <v>1.938</v>
       </c>
       <c r="T48" t="n">
-        <v>282</v>
+        <v>130</v>
       </c>
       <c r="U48" t="n">
-        <v>0.739</v>
+        <v>0.25</v>
       </c>
       <c r="V48" t="n">
-        <v>1.478</v>
+        <v>1.625</v>
       </c>
       <c r="W48" t="n">
-        <v>0.261</v>
+        <v>0.125</v>
       </c>
       <c r="X48" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="Y48" t="n">
-        <v>3.826</v>
+        <v>3.438</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.043</v>
+        <v>5.125</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.759</v>
+        <v>0.671</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.435</v>
+        <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.174</v>
+        <v>1.812</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.37</v>
+        <v>0.552</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.348</v>
+        <v>1</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.174</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>8.784000000000001</v>
+        <v>7.382</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.471</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.55</v>
+        <v>0.604</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.916</v>
+        <v>1.024</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.168</v>
+        <v>0.152</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.388</v>
+        <v>0.418</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.176</v>
+        <v>0.333</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.181</v>
+        <v>0.236</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.133</v>
+        <v>0.117</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.202</v>
+        <v>0.163</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.063</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#15 J. RODRÍGUEZ (Per Game)</t>
+          <t>#14 B. DUBLJEVIC (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" t="n">
-        <v>8.356999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1.815</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>3.481</v>
       </c>
       <c r="F49" t="n">
-        <v>0.964</v>
+        <v>0.481</v>
       </c>
       <c r="G49" t="n">
-        <v>2.821</v>
+        <v>2.185</v>
       </c>
       <c r="H49" t="n">
-        <v>1.464</v>
+        <v>2.296</v>
       </c>
       <c r="I49" t="n">
-        <v>1.821</v>
+        <v>2.852</v>
       </c>
       <c r="J49" t="n">
-        <v>2.643</v>
+        <v>1.667</v>
       </c>
       <c r="K49" t="n">
-        <v>2.571</v>
+        <v>3.926</v>
       </c>
       <c r="L49" t="n">
-        <v>0.536</v>
+        <v>2.593</v>
       </c>
       <c r="M49" t="n">
-        <v>1.107</v>
+        <v>0.63</v>
       </c>
       <c r="N49" t="n">
-        <v>0.786</v>
+        <v>0.481</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.75</v>
+        <v>1.481</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.75</v>
+        <v>1.481</v>
       </c>
       <c r="R49" t="n">
-        <v>2.143</v>
+        <v>2.296</v>
       </c>
       <c r="S49" t="n">
-        <v>1.857</v>
+        <v>2.926</v>
       </c>
       <c r="T49" t="n">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="U49" t="n">
-        <v>0.429</v>
+        <v>0.63</v>
       </c>
       <c r="V49" t="n">
-        <v>0.929</v>
+        <v>1.667</v>
       </c>
       <c r="W49" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>0.75</v>
       </c>
-      <c r="X49" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.857</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4.214</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AK49" t="n">
-        <v>0.464</v>
+        <v>0.37</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.821</v>
+        <v>2.037</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.255</v>
+        <v>0.182</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>9.372999999999999</v>
+        <v>8.403</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.505</v>
+        <v>0.448</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.548</v>
+        <v>0.532</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.892</v>
+        <v>0.877</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.187</v>
+        <v>0.176</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.215</v>
+        <v>0.405</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.51</v>
+        <v>1.125</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.207</v>
+        <v>0.172</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.031</v>
+        <v>0.136</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.142</v>
+        <v>0.206</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.097</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#17 C. ALÍAS (Per Game)</t>
+          <t>#15 J. RODRÍGUEZ (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>8.406000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>2.031</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>4.125</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3.125</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1.438</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1.844</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>2.656</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.25</v>
+        <v>1.656</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.25</v>
+        <v>1.656</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.969</v>
       </c>
       <c r="T50" t="n">
-        <v>-1</v>
+        <v>321</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.188</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.844</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>4.281</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.156</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>2.125</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.221</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>0.25</v>
+        <v>9.717000000000001</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.481</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>0.865</v>
       </c>
       <c r="AS50" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.604</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.249</v>
+        <v>0.206</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>#18 A. SAVKOV (Per Game)</t>
+          <t>#17 C. ALÍAS (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -8169,7 +8169,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -8196,19 +8196,19 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R51" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -8262,18 +8262,18 @@
         <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
         <v>0</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>00:21</t>
+          <t>00:27</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AP51" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT51" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.419</v>
+        <v>0.246</v>
       </c>
       <c r="AW51" t="n">
         <v>0</v>
@@ -8309,338 +8309,338 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>#20 D. STEPHENS (Per Game)</t>
+          <t>#18 A. SAVKOV (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>4.905</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.571</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="H52" t="n">
-        <v>0.476</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1.524</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.476</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.476</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.381</v>
+        <v>0.25</v>
       </c>
       <c r="S52" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>106</v>
+        <v>-2</v>
       </c>
       <c r="U52" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.286</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.381</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.333</v>
+        <v>0.25</v>
       </c>
       <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>00:16</t>
+        </is>
+      </c>
+      <c r="AO52" t="n">
         <v>0.25</v>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>4.299</v>
-      </c>
       <c r="AP52" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.141</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.123</v>
+        <v>0.415</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>#21 C. KOUMADJE (Per Game)</t>
+          <t>#20 D. STEPHENS (Per Game)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>4.682</v>
       </c>
       <c r="D53" t="n">
-        <v>1.529</v>
+        <v>1.091</v>
       </c>
       <c r="E53" t="n">
-        <v>2.294</v>
+        <v>1.5</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1.909</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.455</v>
       </c>
       <c r="I53" t="n">
-        <v>1.765</v>
+        <v>0.545</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="K53" t="n">
-        <v>1.529</v>
+        <v>1.455</v>
       </c>
       <c r="L53" t="n">
-        <v>1.294</v>
+        <v>0.636</v>
       </c>
       <c r="M53" t="n">
-        <v>0.118</v>
+        <v>0.409</v>
       </c>
       <c r="N53" t="n">
-        <v>0.647</v>
+        <v>0.318</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.824</v>
+        <v>0.455</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.824</v>
+        <v>0.455</v>
       </c>
       <c r="R53" t="n">
-        <v>1.882</v>
+        <v>1.318</v>
       </c>
       <c r="S53" t="n">
-        <v>1.294</v>
+        <v>0.636</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="U53" t="n">
-        <v>0.059</v>
+        <v>0.727</v>
       </c>
       <c r="V53" t="n">
-        <v>1.647</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="W53" t="n">
-        <v>0.118</v>
+        <v>0.182</v>
       </c>
       <c r="X53" t="n">
-        <v>0.059</v>
+        <v>0.182</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.118</v>
+        <v>1.227</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.294</v>
+        <v>1.364</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.643</v>
+        <v>0.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.294</v>
+        <v>0.091</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.588</v>
+        <v>0.136</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.059</v>
+        <v>0.227</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.176</v>
+        <v>0.545</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.333</v>
+        <v>0.417</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.273</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>3.894</v>
+        <v>4.104</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.667</v>
+        <v>0.62</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.651</v>
+        <v>0.642</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.027</v>
+        <v>1.141</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.211</v>
+        <v>0.111</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.41</v>
+        <v>0.133</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.165</v>
+        <v>0.122</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.143</v>
+        <v>0.048</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.162</v>
+        <v>0.111</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>#23 Y. TRAORÉ (Per Game)</t>
+          <t>#21 C. KOUMADJE (Per Game)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C54" t="n">
-        <v>0.909</v>
+        <v>3.579</v>
       </c>
       <c r="D54" t="n">
-        <v>0.364</v>
+        <v>1.368</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8179999999999999</v>
+        <v>2.053</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -8649,82 +8649,82 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.182</v>
+        <v>0.842</v>
       </c>
       <c r="I54" t="n">
-        <v>0.591</v>
+        <v>1.684</v>
       </c>
       <c r="J54" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.182</v>
+        <v>1.368</v>
       </c>
       <c r="L54" t="n">
-        <v>0.364</v>
+        <v>1.158</v>
       </c>
       <c r="M54" t="n">
-        <v>0.045</v>
+        <v>0.105</v>
       </c>
       <c r="N54" t="n">
-        <v>0.136</v>
+        <v>0.579</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.227</v>
+        <v>0.737</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.227</v>
+        <v>0.737</v>
       </c>
       <c r="R54" t="n">
-        <v>0.591</v>
+        <v>1.895</v>
       </c>
       <c r="S54" t="n">
-        <v>0.318</v>
+        <v>1.211</v>
       </c>
       <c r="T54" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="U54" t="n">
-        <v>0.182</v>
+        <v>0.053</v>
       </c>
       <c r="V54" t="n">
-        <v>0.136</v>
+        <v>1.474</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.545</v>
+        <v>1.895</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.182</v>
+        <v>3.053</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.462</v>
+        <v>0.621</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.227</v>
+        <v>0.526</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH54" t="n">
         <v>0</v>
@@ -8746,60 +8746,60 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>02:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>1.305</v>
+        <v>3.531</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.444</v>
+        <v>0.667</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.422</v>
+        <v>0.641</v>
       </c>
       <c r="AR54" t="n">
-        <v>0.696</v>
+        <v>1.014</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.174</v>
+        <v>0.209</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.222</v>
+        <v>0.41</v>
       </c>
       <c r="AU54" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.145</v>
+        <v>0.134</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="AY54" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#23 Y. TRAORÉ (Per Game)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -8808,49 +8808,49 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="K55" t="n">
-        <v>1.429</v>
+        <v>0.192</v>
       </c>
       <c r="L55" t="n">
-        <v>1.321</v>
+        <v>0.308</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.143</v>
+        <v>0.231</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="R55" t="n">
-        <v>0.214</v>
+        <v>0.577</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
@@ -8859,22 +8859,22 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.038</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -8905,41 +8905,41 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:52</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="56">
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -8976,10 +8976,10 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.344</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -8991,19 +8991,19 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="AP56" t="n">
         <v>0</v>
@@ -9108,153 +9108,153 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C57" t="n">
-        <v>87.607</v>
+        <v>86.78100000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>22.357</v>
+        <v>22.625</v>
       </c>
       <c r="E57" t="n">
-        <v>39.786</v>
+        <v>40.406</v>
       </c>
       <c r="F57" t="n">
-        <v>7.893</v>
+        <v>7.719</v>
       </c>
       <c r="G57" t="n">
-        <v>24.071</v>
+        <v>24.406</v>
       </c>
       <c r="H57" t="n">
-        <v>19.214</v>
+        <v>18.375</v>
       </c>
       <c r="I57" t="n">
-        <v>24.643</v>
+        <v>23.75</v>
       </c>
       <c r="J57" t="n">
-        <v>16.286</v>
+        <v>16.25</v>
       </c>
       <c r="K57" t="n">
-        <v>24.714</v>
+        <v>24.219</v>
       </c>
       <c r="L57" t="n">
-        <v>11.143</v>
+        <v>11.656</v>
       </c>
       <c r="M57" t="n">
-        <v>7.179</v>
+        <v>7.688</v>
       </c>
       <c r="N57" t="n">
-        <v>6.036</v>
+        <v>6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>15.107</v>
+        <v>15.406</v>
       </c>
       <c r="Q57" t="n">
-        <v>13.964</v>
+        <v>14.156</v>
       </c>
       <c r="R57" t="n">
-        <v>23.107</v>
+        <v>22.938</v>
       </c>
       <c r="S57" t="n">
-        <v>22.607</v>
+        <v>22.344</v>
       </c>
       <c r="T57" t="n">
-        <v>2753</v>
+        <v>3096</v>
       </c>
       <c r="U57" t="n">
-        <v>10.714</v>
+        <v>11.156</v>
       </c>
       <c r="V57" t="n">
-        <v>11.25</v>
+        <v>11.812</v>
       </c>
       <c r="W57" t="n">
-        <v>6.75</v>
+        <v>6.344</v>
       </c>
       <c r="X57" t="n">
-        <v>4.286</v>
+        <v>4.031</v>
       </c>
       <c r="Y57" t="n">
-        <v>33.964</v>
+        <v>33.156</v>
       </c>
       <c r="Z57" t="n">
-        <v>45.321</v>
+        <v>44.438</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.393</v>
+        <v>4.719</v>
       </c>
       <c r="AC57" t="n">
-        <v>10.321</v>
+        <v>10.938</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.426</v>
+        <v>0.431</v>
       </c>
       <c r="AE57" t="n">
-        <v>3.214</v>
+        <v>3.125</v>
       </c>
       <c r="AF57" t="n">
-        <v>8.786</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.366</v>
+        <v>0.356</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.679</v>
+        <v>2.75</v>
       </c>
       <c r="AI57" t="n">
-        <v>6.036</v>
+        <v>6.281</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.444</v>
+        <v>0.438</v>
       </c>
       <c r="AK57" t="n">
-        <v>5.214</v>
+        <v>4.969</v>
       </c>
       <c r="AL57" t="n">
-        <v>18.036</v>
+        <v>18.125</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.289</v>
+        <v>0.274</v>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>200:53</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>89.807</v>
+        <v>90.669</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.536</v>
+        <v>0.528</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.586</v>
+        <v>0.577</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.976</v>
+        <v>0.957</v>
       </c>
       <c r="AS57" t="n">
-        <v>0.168</v>
+        <v>0.17</v>
       </c>
       <c r="AT57" t="n">
-        <v>0.301</v>
+        <v>0.284</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.078</v>
+        <v>1.055</v>
       </c>
       <c r="AV57" t="n">
         <v>0.2</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="AX57" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="AY57" t="n">
         <v>0</v>
@@ -9267,153 +9267,153 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C58" t="n">
-        <v>93.143</v>
+        <v>93.188</v>
       </c>
       <c r="D58" t="n">
-        <v>21.393</v>
+        <v>21.344</v>
       </c>
       <c r="E58" t="n">
-        <v>36.464</v>
+        <v>36.156</v>
       </c>
       <c r="F58" t="n">
-        <v>10.536</v>
+        <v>10.719</v>
       </c>
       <c r="G58" t="n">
-        <v>29.679</v>
+        <v>29.812</v>
       </c>
       <c r="H58" t="n">
-        <v>18.75</v>
+        <v>18.344</v>
       </c>
       <c r="I58" t="n">
-        <v>24.714</v>
+        <v>23.938</v>
       </c>
       <c r="J58" t="n">
-        <v>19.571</v>
+        <v>19.969</v>
       </c>
       <c r="K58" t="n">
-        <v>23.393</v>
+        <v>23.75</v>
       </c>
       <c r="L58" t="n">
-        <v>11.214</v>
+        <v>11.188</v>
       </c>
       <c r="M58" t="n">
-        <v>8.75</v>
+        <v>8.968999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>5.857</v>
+        <v>5.812</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>12.5</v>
+        <v>13.312</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>12.781</v>
       </c>
       <c r="R58" t="n">
-        <v>22.5</v>
+        <v>22.281</v>
       </c>
       <c r="S58" t="n">
-        <v>22.75</v>
+        <v>22.562</v>
       </c>
       <c r="T58" t="n">
-        <v>3066</v>
+        <v>3531</v>
       </c>
       <c r="U58" t="n">
-        <v>15.357</v>
+        <v>15.375</v>
       </c>
       <c r="V58" t="n">
-        <v>11.429</v>
+        <v>11.312</v>
       </c>
       <c r="W58" t="n">
-        <v>7.321</v>
+        <v>7.875</v>
       </c>
       <c r="X58" t="n">
+        <v>4.656</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>32.562</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>43.594</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="AB58" t="n">
         <v>4.25</v>
       </c>
-      <c r="Y58" t="n">
-        <v>33.143</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>44.929</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>4.143</v>
-      </c>
       <c r="AC58" t="n">
-        <v>9.821</v>
+        <v>10.219</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.422</v>
+        <v>0.416</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.857</v>
+        <v>2.875</v>
       </c>
       <c r="AF58" t="n">
-        <v>6.429</v>
+        <v>6.281</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.444</v>
+        <v>0.458</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.321</v>
+        <v>2.5</v>
       </c>
       <c r="AI58" t="n">
-        <v>6.893</v>
+        <v>7.375</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="AK58" t="n">
-        <v>8.214</v>
+        <v>8.218999999999999</v>
       </c>
       <c r="AL58" t="n">
-        <v>22.786</v>
+        <v>22.438</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>200:53</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO58" t="n">
-        <v>89.517</v>
+        <v>89.81399999999999</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.605</v>
+        <v>0.609</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.041</v>
+        <v>1.038</v>
       </c>
       <c r="AS58" t="n">
-        <v>0.14</v>
+        <v>0.148</v>
       </c>
       <c r="AT58" t="n">
-        <v>0.283</v>
+        <v>0.278</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.566</v>
+        <v>1.5</v>
       </c>
       <c r="AV58" t="n">
-        <v>0.199</v>
+        <v>0.198</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="AX58" t="n">
-        <v>0.13</v>
+        <v>0.134</v>
       </c>
       <c r="AY58" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Casademont Zaragoza.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Casademont Zaragoza.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2528.4</v>
+        <v>2684.24</v>
       </c>
       <c r="C2" t="n">
-        <v>2522.220000000001</v>
+        <v>2680.100000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>110.1014185915582</v>
+        <v>110.5182642438714</v>
       </c>
       <c r="E2" t="n">
-        <v>118.2291790565454</v>
+        <v>118.5030409313085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5277242044358728</v>
+        <v>0.5281434407625964</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1699179706348659</v>
+        <v>0.1680595930232558</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3292144748455428</v>
+        <v>0.3289256198347107</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2835101253616201</v>
+        <v>0.2882433045846573</v>
       </c>
       <c r="J2" t="n">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="L2" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="M2" t="n">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="N2" t="n">
-        <v>1061</v>
+        <v>1138</v>
       </c>
       <c r="O2" t="n">
-        <v>1422</v>
+        <v>1535</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6856316297010607</v>
+        <v>0.6967771221062188</v>
       </c>
       <c r="Q2" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="R2" t="n">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1687560270009643</v>
+        <v>0.1661370857921017</v>
       </c>
       <c r="T2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="U2" t="n">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1354869816779171</v>
+        <v>0.1375397185655924</v>
       </c>
       <c r="W2" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="X2" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09691417550626807</v>
+        <v>0.09487063095778484</v>
       </c>
       <c r="Z2" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="AA2" t="n">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2796528447444552</v>
+        <v>0.277349069450749</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7461322081575246</v>
+        <v>0.7413680781758958</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4314285714285714</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3558718861209965</v>
+        <v>0.363036303630363</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4378109452736318</v>
+        <v>0.4449760765550239</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2741379310344828</v>
+        <v>0.2782324058919803</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.492264416315049</v>
+        <v>1.482736156351792</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7117437722419929</v>
+        <v>0.7260726072607261</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9487836107554417</v>
+        <v>0.9621951219512195</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8637362637362638</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.013404825737265</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.573643410852713</v>
+        <v>1.601449275362319</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.054766734279919</v>
+        <v>1.077220077220077</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.206896551724138</v>
+        <v>4.252895752895753</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.261663286004056</v>
+        <v>5.33011583011583</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.0125</v>
+        <v>78.94823529411765</v>
       </c>
       <c r="C3" t="n">
-        <v>78.81937500000004</v>
+        <v>78.82647058823534</v>
       </c>
       <c r="D3" t="n">
-        <v>110.1014185915582</v>
+        <v>110.5182642438714</v>
       </c>
       <c r="E3" t="n">
-        <v>118.2291790565454</v>
+        <v>118.5030409313084</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5277242044358728</v>
+        <v>0.5281434407625964</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1699179706348659</v>
+        <v>0.1680595930232558</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3292144748455428</v>
+        <v>0.3289256198347107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2835101253616201</v>
+        <v>0.2882433045846572</v>
       </c>
       <c r="J3" t="n">
-        <v>11.15625</v>
+        <v>11.55882352941176</v>
       </c>
       <c r="K3" t="n">
-        <v>11.8125</v>
+        <v>11.70588235294118</v>
       </c>
       <c r="L3" t="n">
-        <v>6.34375</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>14.15625</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>33.15625</v>
+        <v>33.47058823529412</v>
       </c>
       <c r="O3" t="n">
-        <v>44.4375</v>
+        <v>45.14705882352941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6856316297010607</v>
+        <v>0.6967771221062188</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.71875</v>
+        <v>4.588235294117647</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9375</v>
+        <v>10.76470588235294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1687560270009643</v>
+        <v>0.1661370857921017</v>
       </c>
       <c r="T3" t="n">
-        <v>3.125</v>
+        <v>3.235294117647059</v>
       </c>
       <c r="U3" t="n">
-        <v>8.78125</v>
+        <v>8.911764705882353</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1354869816779171</v>
+        <v>0.1375397185655924</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.735294117647059</v>
       </c>
       <c r="X3" t="n">
-        <v>6.28125</v>
+        <v>6.147058823529412</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09691417550626807</v>
+        <v>0.09487063095778484</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.96875</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.125</v>
+        <v>17.97058823529412</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2796528447444552</v>
+        <v>0.2773490694507489</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7461322081575246</v>
+        <v>0.7413680781758957</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4314285714285714</v>
+        <v>0.4262295081967212</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3558718861209965</v>
+        <v>0.363036303630363</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4378109452736318</v>
+        <v>0.4449760765550239</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2741379310344828</v>
+        <v>0.2782324058919804</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.492264416315049</v>
+        <v>1.482736156351791</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7117437722419929</v>
+        <v>0.7260726072607261</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9487836107554417</v>
+        <v>0.9621951219512196</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8637362637362637</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.013404825737265</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.573643410852713</v>
+        <v>1.601449275362319</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.054766734279919</v>
+        <v>1.077220077220077</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.206896551724138</v>
+        <v>4.252895752895753</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.261663286004056</v>
+        <v>5.33011583011583</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2516.04</v>
+        <v>2675.959999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>2522.220000000001</v>
+        <v>2680.100000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>118.2291790565454</v>
+        <v>118.5030409313085</v>
       </c>
       <c r="E4" t="n">
-        <v>110.1014185915582</v>
+        <v>110.5182642438714</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5672666982472762</v>
+        <v>0.5699643493761141</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1482234067723483</v>
+        <v>0.1489381203027208</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3159752868490733</v>
+        <v>0.3155703580349709</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2780672666982473</v>
+        <v>0.2754010695187166</v>
       </c>
       <c r="J4" t="n">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="K4" t="n">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="L4" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="M4" t="n">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="N4" t="n">
-        <v>1042</v>
+        <v>1097</v>
       </c>
       <c r="O4" t="n">
-        <v>1395</v>
+        <v>1474</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6608242539081004</v>
+        <v>0.6568627450980392</v>
       </c>
       <c r="Q4" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R4" t="n">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1549028896257698</v>
+        <v>0.1510695187165775</v>
       </c>
       <c r="T4" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="U4" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09521553765987684</v>
+        <v>0.09893048128342247</v>
       </c>
       <c r="W4" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="X4" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1117953576504026</v>
+        <v>0.1118538324420677</v>
       </c>
       <c r="Z4" t="n">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="AA4" t="n">
-        <v>718</v>
+        <v>767</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3401231643770725</v>
+        <v>0.3418003565062389</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7469534050179212</v>
+        <v>0.7442333785617368</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4159021406727829</v>
+        <v>0.4129793510324484</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4577114427860697</v>
+        <v>0.4459459459459459</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3389830508474576</v>
+        <v>0.3426294820717131</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3662952646239555</v>
+        <v>0.3754889178617992</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.493906810035842</v>
+        <v>1.488466757123474</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.9154228855721394</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.078616352201258</v>
+        <v>1.102161100196464</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9979716024340771</v>
+        <v>0.9922779922779923</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.011173184357542</v>
+        <v>1.010554089709762</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.691275167785235</v>
+        <v>1.687898089171975</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.5</v>
+        <v>1.49010989010989</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.955399061032864</v>
+        <v>4.931868131868132</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.455399061032864</v>
+        <v>6.421978021978022</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.62624999999998</v>
+        <v>78.70470588235291</v>
       </c>
       <c r="C5" t="n">
-        <v>78.81937500000004</v>
+        <v>78.82647058823534</v>
       </c>
       <c r="D5" t="n">
-        <v>118.2291790565454</v>
+        <v>118.5030409313084</v>
       </c>
       <c r="E5" t="n">
-        <v>110.1014185915582</v>
+        <v>110.5182642438714</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5672666982472762</v>
+        <v>0.5699643493761141</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1482234067723483</v>
+        <v>0.1489381203027208</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3159752868490733</v>
+        <v>0.3155703580349709</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2780672666982473</v>
+        <v>0.2754010695187166</v>
       </c>
       <c r="J5" t="n">
-        <v>15.375</v>
+        <v>15.11764705882353</v>
       </c>
       <c r="K5" t="n">
-        <v>11.3125</v>
+        <v>11.26470588235294</v>
       </c>
       <c r="L5" t="n">
-        <v>7.875</v>
+        <v>7.794117647058823</v>
       </c>
       <c r="M5" t="n">
-        <v>12.78125</v>
+        <v>12.85294117647059</v>
       </c>
       <c r="N5" t="n">
-        <v>32.5625</v>
+        <v>32.26470588235294</v>
       </c>
       <c r="O5" t="n">
-        <v>43.59375</v>
+        <v>43.35294117647059</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6608242539081004</v>
+        <v>0.6568627450980392</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>4.117647058823529</v>
       </c>
       <c r="R5" t="n">
-        <v>10.21875</v>
+        <v>9.970588235294118</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1549028896257698</v>
+        <v>0.1510695187165775</v>
       </c>
       <c r="T5" t="n">
-        <v>2.875</v>
+        <v>2.911764705882353</v>
       </c>
       <c r="U5" t="n">
-        <v>6.28125</v>
+        <v>6.529411764705882</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09521553765987684</v>
+        <v>0.09893048128342245</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.529411764705882</v>
       </c>
       <c r="X5" t="n">
-        <v>7.375</v>
+        <v>7.382352941176471</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1117953576504026</v>
+        <v>0.1118538324420677</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.21875</v>
+        <v>8.470588235294118</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.4375</v>
+        <v>22.55882352941176</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3401231643770725</v>
+        <v>0.3418003565062389</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7469534050179212</v>
+        <v>0.7442333785617368</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4159021406727829</v>
+        <v>0.4129793510324483</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4577114427860697</v>
+        <v>0.4459459459459459</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3389830508474576</v>
+        <v>0.3426294820717131</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3662952646239555</v>
+        <v>0.3754889178617992</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.493906810035842</v>
+        <v>1.488466757123474</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.9154228855721394</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.078616352201258</v>
+        <v>1.102161100196464</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9979716024340771</v>
+        <v>0.9922779922779923</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.011173184357542</v>
+        <v>1.010554089709763</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.691275167785235</v>
+        <v>1.687898089171975</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.5</v>
+        <v>1.49010989010989</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.955399061032864</v>
+        <v>4.931868131868132</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.455399061032864</v>
+        <v>6.421978021978021</v>
       </c>
     </row>
     <row r="7">
@@ -1419,40 +1419,40 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>234</v>
+      </c>
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
-        <v>203</v>
-      </c>
-      <c r="D8" t="n">
-        <v>28</v>
-      </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H8" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="J8" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="K8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M8" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N8" t="n">
         <v>9</v>
@@ -1461,40 +1461,40 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="R8" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="S8" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T8" t="n">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="U8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="V8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="W8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="Z8" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.78</v>
+        <v>0.794</v>
       </c>
       <c r="AB8" t="n">
         <v>6</v>
@@ -1506,69 +1506,69 @@
         <v>0.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.263</v>
+        <v>0.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.45</v>
+        <v>0.476</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.272</v>
+        <v>0.291</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>711:54</t>
+          <t>752:31</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>249.72</v>
+        <v>270</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.431</v>
+        <v>0.459</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.506</v>
+        <v>0.539</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="AS8" t="n">
         <v>0.196</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.312</v>
+        <v>0.353</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.388</v>
+        <v>2.415</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.155</v>
+        <v>0.159</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="AX8" t="n">
         <v>0.065</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.128</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="9">
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="D9" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E9" t="n">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H9" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="J9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R9" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="S9" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="T9" t="n">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="U9" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="V9" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="W9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="Z9" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.793</v>
+        <v>0.797</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.426</v>
+        <v>0.422</v>
       </c>
       <c r="AE9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AF9" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.411</v>
+        <v>0.404</v>
       </c>
       <c r="AH9" t="n">
         <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.4</v>
+        <v>0.364</v>
       </c>
       <c r="AK9" t="n">
         <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>826:01</t>
+          <t>885:02</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>421.36</v>
+        <v>449.76</v>
       </c>
       <c r="AP9" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AU9" t="n">
         <v>0.603</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.092</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.5610000000000001</v>
-      </c>
       <c r="AV9" t="n">
-        <v>0.226</v>
+        <v>0.225</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.181</v>
+        <v>0.184</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="10">
@@ -1737,91 +1737,91 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I10" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J10" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K10" t="n">
         <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
+        <v>29</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>74</v>
+      </c>
+      <c r="R10" t="n">
+        <v>59</v>
+      </c>
+      <c r="S10" t="n">
+        <v>95</v>
+      </c>
+      <c r="T10" t="n">
+        <v>323</v>
+      </c>
+      <c r="U10" t="n">
+        <v>53</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22</v>
+      </c>
+      <c r="W10" t="n">
         <v>26</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>69</v>
-      </c>
-      <c r="R10" t="n">
-        <v>53</v>
-      </c>
-      <c r="S10" t="n">
-        <v>84</v>
-      </c>
-      <c r="T10" t="n">
-        <v>287</v>
-      </c>
-      <c r="U10" t="n">
-        <v>49</v>
-      </c>
-      <c r="V10" t="n">
-        <v>21</v>
-      </c>
-      <c r="W10" t="n">
-        <v>16</v>
-      </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="Z10" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.752</v>
+        <v>0.737</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3</v>
+        <v>0.311</v>
       </c>
       <c r="AE10" t="n">
         <v>4</v>
@@ -1833,60 +1833,60 @@
         <v>0.286</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.317</v>
+        <v>0.328</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>500:33</t>
+          <t>553:27</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>305.2</v>
+        <v>333.16</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.515</v>
+        <v>0.523</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.576</v>
+        <v>0.581</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.891</v>
+        <v>0.903</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AT10" t="n">
         <v>0.323</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.29</v>
+        <v>1.324</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="11">
@@ -2042,7 +2042,7 @@
         <v>0.021</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="AY11" t="n">
         <v>0.006</v>
@@ -2055,34 +2055,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>5</v>
@@ -2091,31 +2091,31 @@
         <v>9</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S12" t="n">
+        <v>30</v>
+      </c>
+      <c r="T12" t="n">
+        <v>120</v>
+      </c>
+      <c r="U12" t="n">
         <v>26</v>
       </c>
-      <c r="T12" t="n">
-        <v>103</v>
-      </c>
-      <c r="U12" t="n">
-        <v>22</v>
-      </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
         <v>12</v>
@@ -2124,31 +2124,31 @@
         <v>6</v>
       </c>
       <c r="Y12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Z12" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.766</v>
+        <v>0.754</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.533</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.417</v>
+        <v>0.379</v>
       </c>
       <c r="AH12" t="n">
         <v>3</v>
@@ -2160,51 +2160,51 @@
         <v>0.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.361</v>
+        <v>0.372</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>239:50</t>
+          <t>276:27</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>144.68</v>
+        <v>169.44</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.555</v>
+        <v>0.554</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.581</v>
+        <v>0.58</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.173</v>
+        <v>0.171</v>
       </c>
       <c r="AT12" t="n">
         <v>0.155</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.68</v>
+        <v>0.724</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.267</v>
+        <v>0.271</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="13">
@@ -2214,67 +2214,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E13" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I13" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K13" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M13" t="n">
         <v>31</v>
       </c>
       <c r="N13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R13" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="S13" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="T13" t="n">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="U13" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="V13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W13" t="n">
         <v>45</v>
@@ -2283,87 +2283,87 @@
         <v>35</v>
       </c>
       <c r="Y13" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Z13" t="n">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.777</v>
+        <v>0.773</v>
       </c>
       <c r="AB13" t="n">
         <v>28</v>
       </c>
       <c r="AC13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.491</v>
+        <v>0.467</v>
       </c>
       <c r="AE13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.407</v>
+        <v>0.438</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.263</v>
+        <v>0.267</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>843:03</t>
+          <t>900:08</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>477.32</v>
+        <v>505.84</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.537</v>
+        <v>0.53</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.615</v>
+        <v>0.609</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.075</v>
+        <v>1.071</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.126</v>
+        <v>0.121</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.95</v>
+        <v>0.967</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.251</v>
+        <v>0.249</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.124</v>
+        <v>0.121</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="14">
@@ -2522,7 +2522,7 @@
         <v>0.075</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="15">
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
         <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N16" t="n">
         <v>11</v>
@@ -2739,13 +2739,13 @@
         <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T16" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="U16" t="n">
         <v>32</v>
@@ -2754,19 +2754,19 @@
         <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Z16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.744</v>
+        <v>0.756</v>
       </c>
       <c r="AB16" t="n">
         <v>5</v>
@@ -2778,13 +2778,13 @@
         <v>0.417</v>
       </c>
       <c r="AE16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.316</v>
+        <v>0.35</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
@@ -2799,48 +2799,48 @@
         <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.382</v>
+        <v>0.351</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>593:00</t>
+          <t>624:36</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>138.92</v>
+        <v>143.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.535</v>
+        <v>0.531</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.986</v>
+        <v>0.981</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.125</v>
+        <v>0.137</v>
       </c>
       <c r="AU16" t="n">
         <v>2.545</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="AW16" t="n">
         <v>0.067</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="17">
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.661</v>
+        <v>0.662</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -3168,22 +3168,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
@@ -3198,7 +3198,7 @@
         <v>33</v>
       </c>
       <c r="L19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M19" t="n">
         <v>10</v>
@@ -3216,13 +3216,13 @@
         <v>10</v>
       </c>
       <c r="R19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S19" t="n">
         <v>14</v>
       </c>
       <c r="T19" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U19" t="n">
         <v>3</v>
@@ -3240,10 +3240,10 @@
         <v>34</v>
       </c>
       <c r="Z19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.872</v>
+        <v>0.85</v>
       </c>
       <c r="AB19" t="n">
         <v>2</v>
@@ -3264,13 +3264,13 @@
         <v>0.6</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="AK19" t="n">
         <v>2</v>
@@ -3283,41 +3283,41 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>277:54</t>
+          <t>287:35</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>69.04000000000001</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.652</v>
+        <v>0.655</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.115</v>
+        <v>1.126</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.145</v>
+        <v>0.141</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.25</v>
+        <v>0.241</v>
       </c>
       <c r="AU19" t="n">
         <v>0.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="AW19" t="n">
         <v>0.106</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="20">
@@ -3486,100 +3486,100 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>48</v>
+      </c>
+      <c r="D21" t="n">
+        <v>19</v>
+      </c>
+      <c r="E21" t="n">
+        <v>27</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>16</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
-        <v>32</v>
-      </c>
-      <c r="D21" t="n">
-        <v>13</v>
-      </c>
-      <c r="E21" t="n">
-        <v>17</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>51</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" t="n">
         <v>7</v>
       </c>
-      <c r="L21" t="n">
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="AC21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>33</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -3601,41 +3601,41 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40:01</t>
+          <t>89:49</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>23.52</v>
+        <v>39.04</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.765</v>
+        <v>0.704</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.78</v>
+        <v>0.705</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.361</v>
+        <v>1.23</v>
       </c>
       <c r="AS21" t="n">
         <v>0.128</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.353</v>
+        <v>0.37</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.26</v>
+        <v>0.192</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.028</v>
+        <v>0.075</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.198</v>
+        <v>0.177</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="22">
@@ -3791,7 +3791,7 @@
         <v>0.117</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="AY22" t="n">
         <v>0.006</v>
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
         <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I23" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J23" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K23" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N23" t="n">
         <v>13</v>
@@ -3846,19 +3846,19 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S23" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T23" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="U23" t="n">
         <v>17</v>
@@ -3873,13 +3873,13 @@
         <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Z23" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.737</v>
+        <v>0.719</v>
       </c>
       <c r="AB23" t="n">
         <v>11</v>
@@ -3912,48 +3912,48 @@
         <v>10</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>584:39</t>
+          <t>605:25</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>226.88</v>
+        <v>236.2</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.448</v>
+        <v>0.443</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.532</v>
+        <v>0.525</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.877</v>
+        <v>0.855</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.176</v>
+        <v>0.186</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.405</v>
+        <v>0.401</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.125</v>
+        <v>1.114</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.172</v>
+        <v>0.173</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.206</v>
+        <v>0.208</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="24">
@@ -3963,91 +3963,91 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H24" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I24" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J24" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L24" t="n">
         <v>22</v>
       </c>
       <c r="M24" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q24" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R24" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="S24" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T24" t="n">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V24" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="W24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y24" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="Z24" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.664</v>
+        <v>0.658</v>
       </c>
       <c r="AB24" t="n">
         <v>18</v>
       </c>
       <c r="AC24" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.486</v>
+        <v>0.474</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4059,60 +4059,60 @@
         <v>0.118</v>
       </c>
       <c r="AH24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AK24" t="n">
         <v>16</v>
       </c>
-      <c r="AI24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>15</v>
-      </c>
       <c r="AL24" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.221</v>
+        <v>0.222</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>667:20</t>
+          <t>699:43</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>310.96</v>
+        <v>325.16</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.481</v>
+        <v>0.477</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.521</v>
+        <v>0.52</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.865</v>
+        <v>0.864</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.198</v>
+        <v>0.207</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.604</v>
+        <v>1.618</v>
       </c>
       <c r="AV24" t="n">
         <v>0.206</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.153</v>
+        <v>0.156</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.097</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="25">
@@ -4440,22 +4440,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C27" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
         <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H27" t="n">
         <v>10</v>
@@ -4467,7 +4467,7 @@
         <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L27" t="n">
         <v>14</v>
@@ -4476,7 +4476,7 @@
         <v>9</v>
       </c>
       <c r="N27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U27" t="n">
         <v>16</v>
@@ -4509,13 +4509,13 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="AB27" t="n">
         <v>2</v>
@@ -4539,10 +4539,10 @@
         <v>8</v>
       </c>
       <c r="AI27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.571</v>
+        <v>0.533</v>
       </c>
       <c r="AK27" t="n">
         <v>7</v>
@@ -4555,26 +4555,26 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>328:02</t>
+          <t>337:39</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>90.28</v>
+        <v>93.28</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.62</v>
+        <v>0.609</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.642</v>
+        <v>0.63</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.141</v>
+        <v>1.126</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.111</v>
+        <v>0.107</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AU27" t="n">
         <v>0.4</v>
@@ -4583,10 +4583,10 @@
         <v>0.122</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AY27" t="n">
         <v>0.004</v>
@@ -4742,7 +4742,7 @@
         <v>0.16</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AX28" t="n">
         <v>0.159</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C29" t="n">
         <v>22</v>
@@ -4901,7 +4901,7 @@
         <v>0.188</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="AX29" t="n">
         <v>0.076</v>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -4944,11 +4944,11 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
+        <v>47</v>
+      </c>
+      <c r="L30" t="n">
         <v>44</v>
       </c>
-      <c r="L30" t="n">
-        <v>43</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5076,144 +5076,144 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>2777</v>
+        <v>2962</v>
       </c>
       <c r="D31" t="n">
-        <v>724</v>
+        <v>769</v>
       </c>
       <c r="E31" t="n">
-        <v>1293</v>
+        <v>1383</v>
       </c>
       <c r="F31" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="G31" t="n">
+        <v>820</v>
+      </c>
+      <c r="H31" t="n">
+        <v>635</v>
+      </c>
+      <c r="I31" t="n">
+        <v>821</v>
+      </c>
+      <c r="J31" t="n">
+        <v>558</v>
+      </c>
+      <c r="K31" t="n">
+        <v>822</v>
+      </c>
+      <c r="L31" t="n">
+        <v>398</v>
+      </c>
+      <c r="M31" t="n">
+        <v>261</v>
+      </c>
+      <c r="N31" t="n">
+        <v>205</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>518</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>476</v>
+      </c>
+      <c r="R31" t="n">
         <v>781</v>
       </c>
-      <c r="H31" t="n">
-        <v>588</v>
-      </c>
-      <c r="I31" t="n">
-        <v>760</v>
-      </c>
-      <c r="J31" t="n">
-        <v>520</v>
-      </c>
-      <c r="K31" t="n">
-        <v>775</v>
-      </c>
-      <c r="L31" t="n">
-        <v>373</v>
-      </c>
-      <c r="M31" t="n">
-        <v>246</v>
-      </c>
-      <c r="N31" t="n">
-        <v>192</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>493</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>453</v>
-      </c>
-      <c r="R31" t="n">
-        <v>734</v>
-      </c>
       <c r="S31" t="n">
-        <v>715</v>
+        <v>766</v>
       </c>
       <c r="T31" t="n">
-        <v>3096</v>
+        <v>3316</v>
       </c>
       <c r="U31" t="n">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="V31" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="W31" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="X31" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="Y31" t="n">
-        <v>1061</v>
+        <v>1138</v>
       </c>
       <c r="Z31" t="n">
-        <v>1422</v>
+        <v>1535</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.746</v>
+        <v>0.741</v>
       </c>
       <c r="AB31" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AC31" t="n">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.431</v>
+        <v>0.426</v>
       </c>
       <c r="AE31" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF31" t="n">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.356</v>
+        <v>0.363</v>
       </c>
       <c r="AH31" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.438</v>
+        <v>0.445</v>
       </c>
       <c r="AK31" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="AL31" t="n">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.274</v>
+        <v>0.278</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>2901.4</v>
+        <v>3082.24</v>
       </c>
       <c r="AP31" t="n">
         <v>0.528</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.957</v>
+        <v>0.961</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.055</v>
+        <v>1.077</v>
       </c>
       <c r="AV31" t="n">
         <v>0.2</v>
@@ -5235,144 +5235,144 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>2982</v>
+        <v>3176</v>
       </c>
       <c r="D32" t="n">
-        <v>683</v>
+        <v>718</v>
       </c>
       <c r="E32" t="n">
-        <v>1157</v>
+        <v>1226</v>
       </c>
       <c r="F32" t="n">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="G32" t="n">
-        <v>954</v>
+        <v>1018</v>
       </c>
       <c r="H32" t="n">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="I32" t="n">
-        <v>766</v>
+        <v>809</v>
       </c>
       <c r="J32" t="n">
-        <v>639</v>
+        <v>678</v>
       </c>
       <c r="K32" t="n">
-        <v>760</v>
+        <v>812</v>
       </c>
       <c r="L32" t="n">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="M32" t="n">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="N32" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="Q32" t="n">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="R32" t="n">
-        <v>713</v>
+        <v>762</v>
       </c>
       <c r="S32" t="n">
-        <v>722</v>
+        <v>768</v>
       </c>
       <c r="T32" t="n">
-        <v>3531</v>
+        <v>3752</v>
       </c>
       <c r="U32" t="n">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="V32" t="n">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="W32" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="X32" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y32" t="n">
-        <v>1042</v>
+        <v>1097</v>
       </c>
       <c r="Z32" t="n">
-        <v>1395</v>
+        <v>1474</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.747</v>
+        <v>0.744</v>
       </c>
       <c r="AB32" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AC32" t="n">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.416</v>
+        <v>0.413</v>
       </c>
       <c r="AE32" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="AF32" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.458</v>
+        <v>0.446</v>
       </c>
       <c r="AH32" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.339</v>
+        <v>0.343</v>
       </c>
       <c r="AK32" t="n">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="AL32" t="n">
-        <v>718</v>
+        <v>767</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.366</v>
+        <v>0.375</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>2874.04</v>
+        <v>3054.96</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.609</v>
+        <v>0.611</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.038</v>
+        <v>1.04</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.278</v>
+        <v>0.275</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AV32" t="n">
         <v>0.2</v>
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>14.375</v>
+        <v>14.471</v>
       </c>
       <c r="D34" t="n">
-        <v>5.406</v>
+        <v>5.441</v>
       </c>
       <c r="E34" t="n">
-        <v>8.718999999999999</v>
+        <v>8.824</v>
       </c>
       <c r="F34" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="G34" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="H34" t="n">
-        <v>2.625</v>
+        <v>2.706</v>
       </c>
       <c r="I34" t="n">
-        <v>3.719</v>
+        <v>3.794</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>1.029</v>
       </c>
       <c r="K34" t="n">
-        <v>4.125</v>
+        <v>4.206</v>
       </c>
       <c r="L34" t="n">
-        <v>1.156</v>
+        <v>1.265</v>
       </c>
       <c r="M34" t="n">
-        <v>1.188</v>
+        <v>1.235</v>
       </c>
       <c r="N34" t="n">
-        <v>0.781</v>
+        <v>0.765</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.781</v>
+        <v>1.706</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.781</v>
+        <v>1.706</v>
       </c>
       <c r="R34" t="n">
-        <v>2.781</v>
+        <v>2.794</v>
       </c>
       <c r="S34" t="n">
-        <v>3.281</v>
+        <v>3.324</v>
       </c>
       <c r="T34" t="n">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="U34" t="n">
-        <v>1.906</v>
+        <v>2.088</v>
       </c>
       <c r="V34" t="n">
-        <v>1.844</v>
+        <v>1.853</v>
       </c>
       <c r="W34" t="n">
-        <v>1.062</v>
+        <v>1.059</v>
       </c>
       <c r="X34" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>6.118</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.562</v>
+        <v>7.676</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.793</v>
+        <v>0.797</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.906</v>
+        <v>1.882</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.426</v>
+        <v>0.422</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.219</v>
+        <v>1.235</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.969</v>
+        <v>3.059</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.411</v>
+        <v>0.404</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.4</v>
+        <v>0.364</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>25:48</t>
+          <t>26:01</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>13.167</v>
+        <v>13.228</v>
       </c>
       <c r="AP34" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AU34" t="n">
         <v>0.603</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.092</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0.5610000000000001</v>
-      </c>
       <c r="AV34" t="n">
-        <v>0.226</v>
+        <v>0.225</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.181</v>
+        <v>0.184</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="35">
@@ -5610,156 +5610,156 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>6.344</v>
+        <v>6.882</v>
       </c>
       <c r="D35" t="n">
-        <v>0.875</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>2.25</v>
+        <v>2.265</v>
       </c>
       <c r="F35" t="n">
-        <v>0.969</v>
+        <v>1.029</v>
       </c>
       <c r="G35" t="n">
-        <v>3.156</v>
+        <v>3.147</v>
       </c>
       <c r="H35" t="n">
-        <v>1.688</v>
+        <v>1.912</v>
       </c>
       <c r="I35" t="n">
-        <v>1.969</v>
+        <v>2.206</v>
       </c>
       <c r="J35" t="n">
-        <v>3.656</v>
+        <v>3.765</v>
       </c>
       <c r="K35" t="n">
-        <v>1.281</v>
+        <v>1.265</v>
       </c>
       <c r="L35" t="n">
-        <v>0.594</v>
+        <v>0.618</v>
       </c>
       <c r="M35" t="n">
-        <v>1.094</v>
+        <v>1.118</v>
       </c>
       <c r="N35" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.531</v>
+        <v>1.559</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.531</v>
+        <v>1.559</v>
       </c>
       <c r="R35" t="n">
-        <v>2.281</v>
+        <v>2.353</v>
       </c>
       <c r="S35" t="n">
-        <v>2.156</v>
+        <v>2.265</v>
       </c>
       <c r="T35" t="n">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="U35" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.882</v>
       </c>
       <c r="V35" t="n">
-        <v>0.719</v>
+        <v>0.824</v>
       </c>
       <c r="W35" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="X35" t="n">
-        <v>0.344</v>
+        <v>0.353</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.219</v>
+        <v>2.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.844</v>
+        <v>3.147</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.78</v>
+        <v>0.794</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.781</v>
+        <v>0.735</v>
       </c>
       <c r="AD35" t="n">
         <v>0.24</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.156</v>
+        <v>0.176</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.263</v>
+        <v>0.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.281</v>
+        <v>0.294</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.45</v>
+        <v>0.476</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.531</v>
+        <v>2.529</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.272</v>
+        <v>0.291</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>22:14</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>7.804</v>
+        <v>7.941</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.431</v>
+        <v>0.459</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.506</v>
+        <v>0.539</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="AS35" t="n">
         <v>0.196</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.312</v>
+        <v>0.353</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.388</v>
+        <v>2.415</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.155</v>
+        <v>0.159</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="AX35" t="n">
         <v>0.065</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.128</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="36">
@@ -5769,153 +5769,153 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C36" t="n">
-        <v>13.6</v>
+        <v>13.682</v>
       </c>
       <c r="D36" t="n">
-        <v>3.3</v>
+        <v>3.318</v>
       </c>
       <c r="E36" t="n">
-        <v>6.35</v>
+        <v>6.409</v>
       </c>
       <c r="F36" t="n">
-        <v>1.25</v>
+        <v>1.273</v>
       </c>
       <c r="G36" t="n">
-        <v>3.7</v>
+        <v>3.591</v>
       </c>
       <c r="H36" t="n">
-        <v>3.25</v>
+        <v>3.227</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>4.045</v>
       </c>
       <c r="J36" t="n">
-        <v>4.45</v>
+        <v>4.455</v>
       </c>
       <c r="K36" t="n">
-        <v>1.7</v>
+        <v>1.545</v>
       </c>
       <c r="L36" t="n">
-        <v>0.55</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9</v>
+        <v>0.955</v>
       </c>
       <c r="N36" t="n">
-        <v>1.3</v>
+        <v>1.318</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.45</v>
+        <v>3.364</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.45</v>
+        <v>3.364</v>
       </c>
       <c r="R36" t="n">
-        <v>2.65</v>
+        <v>2.682</v>
       </c>
       <c r="S36" t="n">
-        <v>4.2</v>
+        <v>4.318</v>
       </c>
       <c r="T36" t="n">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="U36" t="n">
-        <v>2.45</v>
+        <v>2.409</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.8</v>
+        <v>1.182</v>
       </c>
       <c r="X36" t="n">
-        <v>0.6</v>
+        <v>0.773</v>
       </c>
       <c r="Y36" t="n">
-        <v>5.75</v>
+        <v>5.727</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.65</v>
+        <v>7.773</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.752</v>
+        <v>0.737</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.6</v>
+        <v>0.636</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>2.045</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.3</v>
+        <v>0.311</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.7</v>
+        <v>0.636</v>
       </c>
       <c r="AG36" t="n">
         <v>0.286</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.25</v>
+        <v>0.273</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.55</v>
+        <v>0.545</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="AK36" t="n">
         <v>1</v>
       </c>
       <c r="AL36" t="n">
-        <v>3.15</v>
+        <v>3.045</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.317</v>
+        <v>0.328</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>25:01</t>
+          <t>25:09</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>15.26</v>
+        <v>15.144</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.515</v>
+        <v>0.523</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.576</v>
+        <v>0.581</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.891</v>
+        <v>0.903</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AT36" t="n">
         <v>0.323</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.29</v>
+        <v>1.324</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY36" t="n">
         <v>0.173</v>
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C37" t="n">
-        <v>11.583</v>
+        <v>11.643</v>
       </c>
       <c r="D37" t="n">
-        <v>3.083</v>
+        <v>3.071</v>
       </c>
       <c r="E37" t="n">
-        <v>5.333</v>
+        <v>5.429</v>
       </c>
       <c r="F37" t="n">
-        <v>1.333</v>
+        <v>1.357</v>
       </c>
       <c r="G37" t="n">
-        <v>3.833</v>
+        <v>3.786</v>
       </c>
       <c r="H37" t="n">
-        <v>1.417</v>
+        <v>1.429</v>
       </c>
       <c r="I37" t="n">
-        <v>1.833</v>
+        <v>1.857</v>
       </c>
       <c r="J37" t="n">
-        <v>1.417</v>
+        <v>1.5</v>
       </c>
       <c r="K37" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="L37" t="n">
-        <v>0.417</v>
+        <v>0.357</v>
       </c>
       <c r="M37" t="n">
-        <v>0.75</v>
+        <v>0.643</v>
       </c>
       <c r="N37" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.083</v>
+        <v>2.071</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.083</v>
+        <v>2.071</v>
       </c>
       <c r="R37" t="n">
-        <v>1.333</v>
+        <v>1.429</v>
       </c>
       <c r="S37" t="n">
-        <v>2.167</v>
+        <v>2.143</v>
       </c>
       <c r="T37" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="U37" t="n">
-        <v>1.833</v>
+        <v>1.857</v>
       </c>
       <c r="V37" t="n">
-        <v>0.167</v>
+        <v>0.357</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="X37" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>3.071</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.917</v>
+        <v>4.071</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.766</v>
+        <v>0.754</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.25</v>
+        <v>1.143</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.533</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.833</v>
+        <v>0.786</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>2.071</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.417</v>
+        <v>0.379</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.25</v>
+        <v>0.214</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.833</v>
+        <v>0.714</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.083</v>
+        <v>1.143</v>
       </c>
       <c r="AL37" t="n">
-        <v>3</v>
+        <v>3.071</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.361</v>
+        <v>0.372</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>12.057</v>
+        <v>12.103</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.555</v>
+        <v>0.554</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.581</v>
+        <v>0.58</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.173</v>
+        <v>0.171</v>
       </c>
       <c r="AT37" t="n">
         <v>0.155</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.68</v>
+        <v>0.724</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.267</v>
+        <v>0.271</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.055</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="38">
@@ -6233,7 +6233,7 @@
         <v>0.021</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="AY38" t="n">
         <v>0.023</v>
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39" t="n">
-        <v>16.031</v>
+        <v>15.941</v>
       </c>
       <c r="D39" t="n">
-        <v>3.438</v>
+        <v>3.412</v>
       </c>
       <c r="E39" t="n">
-        <v>5.906</v>
+        <v>6.029</v>
       </c>
       <c r="F39" t="n">
         <v>1.5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.688</v>
+        <v>4.647</v>
       </c>
       <c r="H39" t="n">
-        <v>4.656</v>
+        <v>4.618</v>
       </c>
       <c r="I39" t="n">
-        <v>5.562</v>
+        <v>5.471</v>
       </c>
       <c r="J39" t="n">
-        <v>1.781</v>
+        <v>1.735</v>
       </c>
       <c r="K39" t="n">
-        <v>2.875</v>
+        <v>2.824</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.971</v>
       </c>
       <c r="M39" t="n">
-        <v>0.969</v>
+        <v>0.912</v>
       </c>
       <c r="N39" t="n">
-        <v>0.906</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.875</v>
+        <v>1.794</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.875</v>
+        <v>1.794</v>
       </c>
       <c r="R39" t="n">
-        <v>2.594</v>
+        <v>2.559</v>
       </c>
       <c r="S39" t="n">
-        <v>4.938</v>
+        <v>4.941</v>
       </c>
       <c r="T39" t="n">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="U39" t="n">
-        <v>2.656</v>
+        <v>2.735</v>
       </c>
       <c r="V39" t="n">
-        <v>2.062</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>1.406</v>
+        <v>1.324</v>
       </c>
       <c r="X39" t="n">
-        <v>1.094</v>
+        <v>1.029</v>
       </c>
       <c r="Y39" t="n">
-        <v>6.875</v>
+        <v>6.794</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.843999999999999</v>
+        <v>8.794</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.777</v>
+        <v>0.773</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.875</v>
+        <v>0.824</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.781</v>
+        <v>1.765</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.491</v>
+        <v>0.467</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.344</v>
+        <v>0.412</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.844</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.407</v>
+        <v>0.438</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.125</v>
+        <v>1.118</v>
       </c>
       <c r="AJ39" t="n">
         <v>0.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.562</v>
+        <v>3.529</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.263</v>
+        <v>0.267</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>26:20</t>
+          <t>26:28</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>14.916</v>
+        <v>14.878</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.537</v>
+        <v>0.53</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.615</v>
+        <v>0.609</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.075</v>
+        <v>1.071</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.126</v>
+        <v>0.121</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.95</v>
+        <v>0.967</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.251</v>
+        <v>0.249</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.124</v>
+        <v>0.121</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="40">
@@ -6723,156 +6723,156 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>4.281</v>
+        <v>4.147</v>
       </c>
       <c r="D42" t="n">
-        <v>0.781</v>
+        <v>0.765</v>
       </c>
       <c r="E42" t="n">
-        <v>1.625</v>
+        <v>1.559</v>
       </c>
       <c r="F42" t="n">
-        <v>0.75</v>
+        <v>0.706</v>
       </c>
       <c r="G42" t="n">
-        <v>2.125</v>
+        <v>2.088</v>
       </c>
       <c r="H42" t="n">
-        <v>0.469</v>
+        <v>0.5</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="J42" t="n">
-        <v>0.875</v>
+        <v>0.824</v>
       </c>
       <c r="K42" t="n">
-        <v>1.969</v>
+        <v>1.971</v>
       </c>
       <c r="L42" t="n">
-        <v>1.094</v>
+        <v>1.088</v>
       </c>
       <c r="M42" t="n">
-        <v>0.656</v>
+        <v>0.647</v>
       </c>
       <c r="N42" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="R42" t="n">
-        <v>2.188</v>
+        <v>2.176</v>
       </c>
       <c r="S42" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="T42" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="V42" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="W42" t="n">
-        <v>0.375</v>
+        <v>0.412</v>
       </c>
       <c r="X42" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.906</v>
+        <v>0.912</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.219</v>
+        <v>1.206</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.744</v>
+        <v>0.756</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="AD42" t="n">
         <v>0.417</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.316</v>
+        <v>0.35</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.062</v>
+        <v>1</v>
       </c>
       <c r="AJ42" t="n">
         <v>0.324</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.062</v>
+        <v>1.088</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.382</v>
+        <v>0.351</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>4.341</v>
+        <v>4.229</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.535</v>
+        <v>0.531</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.986</v>
+        <v>0.981</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.125</v>
+        <v>0.137</v>
       </c>
       <c r="AU42" t="n">
         <v>2.545</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="AW42" t="n">
         <v>0.067</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="43">
@@ -7181,13 +7181,13 @@
         <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="AW44" t="n">
         <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.661</v>
+        <v>0.662</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -7200,156 +7200,156 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C45" t="n">
-        <v>2.406</v>
+        <v>2.353</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="E45" t="n">
-        <v>0.969</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.125</v>
+        <v>0.147</v>
       </c>
       <c r="G45" t="n">
-        <v>0.656</v>
+        <v>0.647</v>
       </c>
       <c r="H45" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="J45" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="K45" t="n">
-        <v>1.031</v>
+        <v>0.971</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="M45" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="N45" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="R45" t="n">
-        <v>1.625</v>
+        <v>1.559</v>
       </c>
       <c r="S45" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="T45" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U45" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="V45" t="n">
-        <v>0.656</v>
+        <v>0.618</v>
       </c>
       <c r="W45" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="X45" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.062</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.219</v>
+        <v>1.176</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.872</v>
+        <v>0.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AD45" t="n">
         <v>0.667</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AG45" t="n">
         <v>0.6</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.062</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="AM45" t="n">
         <v>0.25</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>2.158</v>
+        <v>2.089</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.652</v>
+        <v>0.655</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.115</v>
+        <v>1.126</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.145</v>
+        <v>0.141</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.25</v>
+        <v>0.241</v>
       </c>
       <c r="AU45" t="n">
         <v>0.8</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="AW45" t="n">
         <v>0.106</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="46">
@@ -7518,16 +7518,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="E47" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -7536,19 +7536,19 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I47" t="n">
         <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K47" t="n">
         <v>3.5</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -7560,25 +7560,25 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>51</v>
+      </c>
+      <c r="U47" t="n">
         <v>2.5</v>
       </c>
-      <c r="T47" t="n">
-        <v>33</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3</v>
-      </c>
       <c r="V47" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -7587,31 +7587,31 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>9.5</v>
+        <v>6.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>11.5</v>
+        <v>9.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.826</v>
+        <v>0.73</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AF47" t="n">
         <v>0.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
@@ -7633,41 +7633,41 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>11.76</v>
+        <v>9.76</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.765</v>
+        <v>0.704</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.78</v>
+        <v>0.705</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.361</v>
+        <v>1.23</v>
       </c>
       <c r="AS47" t="n">
         <v>0.128</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.353</v>
+        <v>0.37</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.26</v>
+        <v>0.192</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.028</v>
+        <v>0.075</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.198</v>
+        <v>0.177</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="48">
@@ -7823,7 +7823,7 @@
         <v>0.117</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="AY48" t="n">
         <v>0.014</v>
@@ -7836,156 +7836,156 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C49" t="n">
-        <v>7.37</v>
+        <v>6.966</v>
       </c>
       <c r="D49" t="n">
-        <v>1.815</v>
+        <v>1.724</v>
       </c>
       <c r="E49" t="n">
-        <v>3.481</v>
+        <v>3.345</v>
       </c>
       <c r="F49" t="n">
-        <v>0.481</v>
+        <v>0.448</v>
       </c>
       <c r="G49" t="n">
-        <v>2.185</v>
+        <v>2.069</v>
       </c>
       <c r="H49" t="n">
-        <v>2.296</v>
+        <v>2.172</v>
       </c>
       <c r="I49" t="n">
-        <v>2.852</v>
+        <v>2.759</v>
       </c>
       <c r="J49" t="n">
-        <v>1.667</v>
+        <v>1.69</v>
       </c>
       <c r="K49" t="n">
-        <v>3.926</v>
+        <v>3.828</v>
       </c>
       <c r="L49" t="n">
-        <v>2.593</v>
+        <v>2.448</v>
       </c>
       <c r="M49" t="n">
-        <v>0.63</v>
+        <v>0.621</v>
       </c>
       <c r="N49" t="n">
-        <v>0.481</v>
+        <v>0.448</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.481</v>
+        <v>1.517</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.481</v>
+        <v>1.517</v>
       </c>
       <c r="R49" t="n">
-        <v>2.296</v>
+        <v>2.172</v>
       </c>
       <c r="S49" t="n">
-        <v>2.926</v>
+        <v>2.793</v>
       </c>
       <c r="T49" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="U49" t="n">
-        <v>0.63</v>
+        <v>0.586</v>
       </c>
       <c r="V49" t="n">
-        <v>1.667</v>
+        <v>1.552</v>
       </c>
       <c r="W49" t="n">
-        <v>0.222</v>
+        <v>0.207</v>
       </c>
       <c r="X49" t="n">
-        <v>0.111</v>
+        <v>0.103</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.63</v>
+        <v>3.448</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.926</v>
+        <v>4.793</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.737</v>
+        <v>0.719</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.407</v>
+        <v>0.379</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.111</v>
+        <v>1.034</v>
       </c>
       <c r="AD49" t="n">
         <v>0.367</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.296</v>
+        <v>0.276</v>
       </c>
       <c r="AG49" t="n">
         <v>0.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.111</v>
+        <v>0.103</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="AJ49" t="n">
         <v>0.75</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.37</v>
+        <v>0.345</v>
       </c>
       <c r="AL49" t="n">
-        <v>2.037</v>
+        <v>1.931</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>8.403</v>
+        <v>8.145</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.448</v>
+        <v>0.443</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.532</v>
+        <v>0.525</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.877</v>
+        <v>0.855</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.176</v>
+        <v>0.186</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.405</v>
+        <v>0.401</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.125</v>
+        <v>1.114</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.172</v>
+        <v>0.173</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.206</v>
+        <v>0.208</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="50">
@@ -7995,97 +7995,97 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
-        <v>8.406000000000001</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>2.031</v>
+        <v>1.941</v>
       </c>
       <c r="E50" t="n">
-        <v>4.125</v>
+        <v>4.029</v>
       </c>
       <c r="F50" t="n">
-        <v>0.969</v>
+        <v>0.971</v>
       </c>
       <c r="G50" t="n">
-        <v>3.125</v>
+        <v>3.088</v>
       </c>
       <c r="H50" t="n">
-        <v>1.438</v>
+        <v>1.471</v>
       </c>
       <c r="I50" t="n">
-        <v>1.844</v>
+        <v>1.882</v>
       </c>
       <c r="J50" t="n">
-        <v>2.656</v>
+        <v>2.618</v>
       </c>
       <c r="K50" t="n">
-        <v>2.812</v>
+        <v>2.824</v>
       </c>
       <c r="L50" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="M50" t="n">
-        <v>1.25</v>
+        <v>1.265</v>
       </c>
       <c r="N50" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.656</v>
+        <v>1.618</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.656</v>
+        <v>1.618</v>
       </c>
       <c r="R50" t="n">
-        <v>2.25</v>
+        <v>2.353</v>
       </c>
       <c r="S50" t="n">
-        <v>1.969</v>
+        <v>1.941</v>
       </c>
       <c r="T50" t="n">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U50" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="V50" t="n">
-        <v>1.188</v>
+        <v>1.206</v>
       </c>
       <c r="W50" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="X50" t="n">
         <v>0.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.844</v>
+        <v>2.824</v>
       </c>
       <c r="Z50" t="n">
-        <v>4.281</v>
+        <v>4.294</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.664</v>
+        <v>0.658</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.156</v>
+        <v>1.118</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.486</v>
+        <v>0.474</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="AG50" t="n">
         <v>0.118</v>
@@ -8094,57 +8094,57 @@
         <v>0.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>1</v>
+        <v>0.971</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.125</v>
+        <v>2.118</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.221</v>
+        <v>0.222</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>9.717000000000001</v>
+        <v>9.564</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.481</v>
+        <v>0.477</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.521</v>
+        <v>0.52</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.865</v>
+        <v>0.864</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.198</v>
+        <v>0.207</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.604</v>
+        <v>1.618</v>
       </c>
       <c r="AV50" t="n">
         <v>0.206</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.153</v>
+        <v>0.156</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.097</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="51">
@@ -8472,141 +8472,141 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C53" t="n">
-        <v>4.682</v>
+        <v>4.375</v>
       </c>
       <c r="D53" t="n">
-        <v>1.091</v>
+        <v>1.042</v>
       </c>
       <c r="E53" t="n">
-        <v>1.5</v>
+        <v>1.458</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="G53" t="n">
-        <v>1.909</v>
+        <v>1.792</v>
       </c>
       <c r="H53" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="I53" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
-        <v>0.182</v>
+        <v>0.167</v>
       </c>
       <c r="K53" t="n">
-        <v>1.455</v>
+        <v>1.458</v>
       </c>
       <c r="L53" t="n">
-        <v>0.636</v>
+        <v>0.583</v>
       </c>
       <c r="M53" t="n">
-        <v>0.409</v>
+        <v>0.375</v>
       </c>
       <c r="N53" t="n">
-        <v>0.318</v>
+        <v>0.333</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="R53" t="n">
-        <v>1.318</v>
+        <v>1.208</v>
       </c>
       <c r="S53" t="n">
-        <v>0.636</v>
+        <v>0.583</v>
       </c>
       <c r="T53" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U53" t="n">
-        <v>0.727</v>
+        <v>0.667</v>
       </c>
       <c r="V53" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="W53" t="n">
-        <v>0.182</v>
+        <v>0.167</v>
       </c>
       <c r="X53" t="n">
-        <v>0.182</v>
+        <v>0.167</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.227</v>
+        <v>1.167</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.364</v>
+        <v>1.333</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.091</v>
+        <v>0.083</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.136</v>
+        <v>0.125</v>
       </c>
       <c r="AD53" t="n">
         <v>0.667</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.227</v>
+        <v>0.208</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="AG53" t="n">
         <v>0.417</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.636</v>
+        <v>0.625</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.571</v>
+        <v>0.533</v>
       </c>
       <c r="AK53" t="n">
-        <v>0.318</v>
+        <v>0.292</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.273</v>
+        <v>1.167</v>
       </c>
       <c r="AM53" t="n">
         <v>0.25</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>4.104</v>
+        <v>3.887</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.62</v>
+        <v>0.609</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.642</v>
+        <v>0.63</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.141</v>
+        <v>1.126</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.111</v>
+        <v>0.107</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AU53" t="n">
         <v>0.4</v>
@@ -8615,10 +8615,10 @@
         <v>0.122</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AY53" t="n">
         <v>0.006</v>
@@ -8774,7 +8774,7 @@
         <v>0.16</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AX54" t="n">
         <v>0.159</v>
@@ -8790,16 +8790,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C55" t="n">
-        <v>0.846</v>
+        <v>0.786</v>
       </c>
       <c r="D55" t="n">
-        <v>0.346</v>
+        <v>0.321</v>
       </c>
       <c r="E55" t="n">
-        <v>0.769</v>
+        <v>0.714</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -8808,49 +8808,49 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.464</v>
       </c>
       <c r="J55" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="K55" t="n">
-        <v>0.192</v>
+        <v>0.179</v>
       </c>
       <c r="L55" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="M55" t="n">
-        <v>0.077</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="R55" t="n">
-        <v>0.577</v>
+        <v>0.536</v>
       </c>
       <c r="S55" t="n">
-        <v>0.269</v>
+        <v>0.25</v>
       </c>
       <c r="T55" t="n">
         <v>8</v>
       </c>
       <c r="U55" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="V55" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
@@ -8859,19 +8859,19 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.462</v>
+        <v>0.429</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.038</v>
+        <v>0.964</v>
       </c>
       <c r="AA55" t="n">
         <v>0.444</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="AD55" t="n">
         <v>0.167</v>
@@ -8905,11 +8905,11 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>02:52</t>
+          <t>02:39</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>1.22</v>
+        <v>1.133</v>
       </c>
       <c r="AP55" t="n">
         <v>0.45</v>
@@ -8933,7 +8933,7 @@
         <v>0.188</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="AX55" t="n">
         <v>0.076</v>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -8976,10 +8976,10 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1.375</v>
+        <v>1.382</v>
       </c>
       <c r="L56" t="n">
-        <v>1.344</v>
+        <v>1.294</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -8991,13 +8991,13 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.25</v>
+        <v>1.235</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -9108,144 +9108,144 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C57" t="n">
-        <v>86.78100000000001</v>
+        <v>87.11799999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>22.625</v>
+        <v>22.618</v>
       </c>
       <c r="E57" t="n">
-        <v>40.406</v>
+        <v>40.676</v>
       </c>
       <c r="F57" t="n">
-        <v>7.719</v>
+        <v>7.735</v>
       </c>
       <c r="G57" t="n">
-        <v>24.406</v>
+        <v>24.118</v>
       </c>
       <c r="H57" t="n">
-        <v>18.375</v>
+        <v>18.676</v>
       </c>
       <c r="I57" t="n">
-        <v>23.75</v>
+        <v>24.147</v>
       </c>
       <c r="J57" t="n">
-        <v>16.25</v>
+        <v>16.412</v>
       </c>
       <c r="K57" t="n">
-        <v>24.219</v>
+        <v>24.176</v>
       </c>
       <c r="L57" t="n">
-        <v>11.656</v>
+        <v>11.706</v>
       </c>
       <c r="M57" t="n">
-        <v>7.688</v>
+        <v>7.676</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>6.029</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>15.406</v>
+        <v>15.235</v>
       </c>
       <c r="Q57" t="n">
-        <v>14.156</v>
+        <v>14</v>
       </c>
       <c r="R57" t="n">
-        <v>22.938</v>
+        <v>22.971</v>
       </c>
       <c r="S57" t="n">
-        <v>22.344</v>
+        <v>22.529</v>
       </c>
       <c r="T57" t="n">
-        <v>3096</v>
+        <v>3316</v>
       </c>
       <c r="U57" t="n">
-        <v>11.156</v>
+        <v>11.559</v>
       </c>
       <c r="V57" t="n">
-        <v>11.812</v>
+        <v>11.706</v>
       </c>
       <c r="W57" t="n">
-        <v>6.344</v>
+        <v>6.5</v>
       </c>
       <c r="X57" t="n">
-        <v>4.031</v>
+        <v>4.059</v>
       </c>
       <c r="Y57" t="n">
-        <v>33.156</v>
+        <v>33.471</v>
       </c>
       <c r="Z57" t="n">
-        <v>44.438</v>
+        <v>45.147</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.746</v>
+        <v>0.741</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.719</v>
+        <v>4.588</v>
       </c>
       <c r="AC57" t="n">
-        <v>10.938</v>
+        <v>10.765</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.431</v>
+        <v>0.426</v>
       </c>
       <c r="AE57" t="n">
-        <v>3.125</v>
+        <v>3.235</v>
       </c>
       <c r="AF57" t="n">
-        <v>8.781000000000001</v>
+        <v>8.912000000000001</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.356</v>
+        <v>0.363</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.75</v>
+        <v>2.735</v>
       </c>
       <c r="AI57" t="n">
-        <v>6.281</v>
+        <v>6.147</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.438</v>
+        <v>0.445</v>
       </c>
       <c r="AK57" t="n">
-        <v>4.969</v>
+        <v>5</v>
       </c>
       <c r="AL57" t="n">
-        <v>18.125</v>
+        <v>17.971</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.274</v>
+        <v>0.278</v>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>90.669</v>
+        <v>90.654</v>
       </c>
       <c r="AP57" t="n">
         <v>0.528</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.957</v>
+        <v>0.961</v>
       </c>
       <c r="AS57" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="AT57" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.055</v>
+        <v>1.077</v>
       </c>
       <c r="AV57" t="n">
         <v>0.2</v>
@@ -9267,144 +9267,144 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C58" t="n">
-        <v>93.188</v>
+        <v>93.41200000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>21.344</v>
+        <v>21.118</v>
       </c>
       <c r="E58" t="n">
-        <v>36.156</v>
+        <v>36.059</v>
       </c>
       <c r="F58" t="n">
-        <v>10.719</v>
+        <v>11</v>
       </c>
       <c r="G58" t="n">
-        <v>29.812</v>
+        <v>29.941</v>
       </c>
       <c r="H58" t="n">
-        <v>18.344</v>
+        <v>18.176</v>
       </c>
       <c r="I58" t="n">
-        <v>23.938</v>
+        <v>23.794</v>
       </c>
       <c r="J58" t="n">
-        <v>19.969</v>
+        <v>19.941</v>
       </c>
       <c r="K58" t="n">
-        <v>23.75</v>
+        <v>23.882</v>
       </c>
       <c r="L58" t="n">
-        <v>11.188</v>
+        <v>11.147</v>
       </c>
       <c r="M58" t="n">
-        <v>8.968999999999999</v>
+        <v>8.765000000000001</v>
       </c>
       <c r="N58" t="n">
-        <v>5.812</v>
+        <v>5.912</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>13.312</v>
+        <v>13.382</v>
       </c>
       <c r="Q58" t="n">
-        <v>12.781</v>
+        <v>12.853</v>
       </c>
       <c r="R58" t="n">
-        <v>22.281</v>
+        <v>22.412</v>
       </c>
       <c r="S58" t="n">
-        <v>22.562</v>
+        <v>22.588</v>
       </c>
       <c r="T58" t="n">
-        <v>3531</v>
+        <v>3752</v>
       </c>
       <c r="U58" t="n">
-        <v>15.375</v>
+        <v>15.118</v>
       </c>
       <c r="V58" t="n">
-        <v>11.312</v>
+        <v>11.265</v>
       </c>
       <c r="W58" t="n">
-        <v>7.875</v>
+        <v>7.794</v>
       </c>
       <c r="X58" t="n">
-        <v>4.656</v>
+        <v>4.618</v>
       </c>
       <c r="Y58" t="n">
-        <v>32.562</v>
+        <v>32.265</v>
       </c>
       <c r="Z58" t="n">
-        <v>43.594</v>
+        <v>43.353</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.747</v>
+        <v>0.744</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.25</v>
+        <v>4.118</v>
       </c>
       <c r="AC58" t="n">
-        <v>10.219</v>
+        <v>9.971</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.416</v>
+        <v>0.413</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.875</v>
+        <v>2.912</v>
       </c>
       <c r="AF58" t="n">
-        <v>6.281</v>
+        <v>6.529</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.458</v>
+        <v>0.446</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.5</v>
+        <v>2.529</v>
       </c>
       <c r="AI58" t="n">
-        <v>7.375</v>
+        <v>7.382</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.339</v>
+        <v>0.343</v>
       </c>
       <c r="AK58" t="n">
-        <v>8.218999999999999</v>
+        <v>8.471</v>
       </c>
       <c r="AL58" t="n">
-        <v>22.438</v>
+        <v>22.559</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.366</v>
+        <v>0.375</v>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO58" t="n">
-        <v>89.81399999999999</v>
+        <v>89.852</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.609</v>
+        <v>0.611</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.038</v>
+        <v>1.04</v>
       </c>
       <c r="AS58" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="AT58" t="n">
-        <v>0.278</v>
+        <v>0.275</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AV58" t="n">
         <v>0.198</v>
@@ -9413,7 +9413,7 @@
         <v>0.063</v>
       </c>
       <c r="AX58" t="n">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
       <c r="AY58" t="n">
         <v>0</v>
